--- a/data/import/DONE/AMPHI.xlsx
+++ b/data/import/DONE/AMPHI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7924802-4A81-4A9B-A1E2-57BC325486EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A932AEC8-9C1A-49DE-971C-4F343FF9B06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5518,13 +5518,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5956,7 +5956,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6004,7 +6004,7 @@
       <c r="L5" s="7"/>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -6056,7 +6056,7 @@
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -6104,7 +6104,7 @@
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="15" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -6148,7 +6148,7 @@
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -6196,7 +6196,7 @@
       <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -6244,7 +6244,7 @@
       <c r="L15" s="7"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -6292,7 +6292,7 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="15" t="s">
         <v>39</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -6336,7 +6336,7 @@
       <c r="L19" s="7"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -6384,7 +6384,7 @@
       <c r="L21" s="7"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -6432,7 +6432,7 @@
       <c r="L23" s="7"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -6480,7 +6480,7 @@
       <c r="L25" s="7"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="15" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -6528,7 +6528,7 @@
       <c r="L27" s="7"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="15" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -6576,7 +6576,7 @@
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="15" t="s">
         <v>57</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -6624,7 +6624,7 @@
       <c r="L31" s="7"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -6672,7 +6672,7 @@
       <c r="L33" s="7"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="15" t="s">
         <v>63</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -6720,7 +6720,7 @@
       <c r="L35" s="7"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -6768,7 +6768,7 @@
       <c r="L37" s="7"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="15" t="s">
         <v>69</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -6816,7 +6816,7 @@
       <c r="L39" s="7"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -6864,7 +6864,7 @@
       <c r="L41" s="7"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="15" t="s">
         <v>75</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -6912,7 +6912,7 @@
       <c r="L43" s="7"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="15" t="s">
         <v>78</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -6960,7 +6960,7 @@
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="15" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -7008,7 +7008,7 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="15" t="s">
         <v>84</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -7056,7 +7056,7 @@
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="15" t="s">
         <v>86</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -7100,7 +7100,7 @@
       <c r="L51" s="7"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="15" t="s">
         <v>89</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -7148,7 +7148,7 @@
       <c r="L53" s="7"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -7196,7 +7196,7 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -7244,7 +7244,7 @@
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="15" t="s">
         <v>98</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -7292,7 +7292,7 @@
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -7340,7 +7340,7 @@
       <c r="L61" s="7"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="15" t="s">
         <v>104</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -7392,7 +7392,7 @@
       <c r="L63" s="7"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="15" t="s">
         <v>107</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -7436,7 +7436,7 @@
       <c r="L65" s="7"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -7484,7 +7484,7 @@
       <c r="L67" s="7"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="15" t="s">
         <v>113</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -7520,7 +7520,7 @@
       <c r="L69" s="7"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="15" t="s">
         <v>114</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -7568,7 +7568,7 @@
       <c r="L71" s="7"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -7616,7 +7616,7 @@
       <c r="L73" s="7"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="15" t="s">
         <v>120</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -7660,7 +7660,7 @@
       <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="15" t="s">
         <v>123</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -7704,7 +7704,7 @@
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="15" t="s">
         <v>126</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -7752,7 +7752,7 @@
       <c r="L79" s="7"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="15" t="s">
         <v>129</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -7800,7 +7800,7 @@
       <c r="L81" s="7"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B82" s="8" t="s">
@@ -7848,7 +7848,7 @@
       <c r="L83" s="7"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
+      <c r="A84" s="15" t="s">
         <v>135</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -7896,7 +7896,7 @@
       <c r="L85" s="7"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="17" t="s">
+      <c r="A86" s="15" t="s">
         <v>138</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -7944,7 +7944,7 @@
       <c r="L87" s="7"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="15" t="s">
         <v>141</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -7984,7 +7984,7 @@
       <c r="L89" s="7"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="17" t="s">
+      <c r="A90" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -8020,7 +8020,7 @@
       <c r="L91" s="7"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="15" t="s">
         <v>146</v>
       </c>
       <c r="B92" s="8" t="s">
@@ -8068,7 +8068,7 @@
       <c r="L93" s="7"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="15" t="s">
         <v>149</v>
       </c>
       <c r="B94" s="8" t="s">
@@ -8116,7 +8116,7 @@
       <c r="L95" s="7"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="15" t="s">
         <v>152</v>
       </c>
       <c r="B96" s="8" t="s">
@@ -8164,7 +8164,7 @@
       <c r="L97" s="7"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="17" t="s">
+      <c r="A98" s="15" t="s">
         <v>155</v>
       </c>
       <c r="B98" s="8"/>
@@ -8206,7 +8206,7 @@
       <c r="L99" s="7"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="15" t="s">
         <v>157</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -8242,7 +8242,7 @@
       <c r="L101" s="7"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="15" t="s">
         <v>160</v>
       </c>
       <c r="B102" s="8" t="s">
@@ -8282,7 +8282,7 @@
       <c r="L103" s="7"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="15" t="s">
         <v>163</v>
       </c>
       <c r="B104" s="8" t="s">
@@ -8330,7 +8330,7 @@
       <c r="L105" s="7"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
+      <c r="A106" s="15" t="s">
         <v>166</v>
       </c>
       <c r="B106" s="8" t="s">
@@ -8378,7 +8378,7 @@
       <c r="L107" s="7"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="17" t="s">
+      <c r="A108" s="15" t="s">
         <v>169</v>
       </c>
       <c r="B108" s="8"/>
@@ -8424,7 +8424,7 @@
       <c r="L109" s="7"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -8472,7 +8472,7 @@
       <c r="L111" s="7"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="15" t="s">
         <v>174</v>
       </c>
       <c r="B112" s="8" t="s">
@@ -8520,7 +8520,7 @@
       <c r="L113" s="7"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="15" t="s">
         <v>177</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -8564,7 +8564,7 @@
       <c r="L115" s="7"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="15" t="s">
         <v>180</v>
       </c>
       <c r="B116" s="8" t="s">
@@ -8604,7 +8604,7 @@
       <c r="L117" s="7"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="15" t="s">
         <v>183</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -8652,7 +8652,7 @@
       <c r="L119" s="7"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="17" t="s">
+      <c r="A120" s="15" t="s">
         <v>186</v>
       </c>
       <c r="B120" s="8"/>
@@ -8698,7 +8698,7 @@
       <c r="L121" s="7"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="17" t="s">
+      <c r="A122" s="15" t="s">
         <v>188</v>
       </c>
       <c r="B122" s="8" t="s">
@@ -8746,7 +8746,7 @@
       <c r="L123" s="7"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="17" t="s">
+      <c r="A124" s="15" t="s">
         <v>191</v>
       </c>
       <c r="B124" s="8" t="s">
@@ -8794,7 +8794,7 @@
       <c r="L125" s="7"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="15" t="s">
         <v>194</v>
       </c>
       <c r="B126" s="8" t="s">
@@ -8842,7 +8842,7 @@
       <c r="L127" s="7"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="17" t="s">
+      <c r="A128" s="15" t="s">
         <v>197</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -8878,7 +8878,7 @@
       <c r="L129" s="7"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="17" t="s">
+      <c r="A130" s="15" t="s">
         <v>199</v>
       </c>
       <c r="B130" s="8" t="s">
@@ -8922,7 +8922,7 @@
       <c r="L131" s="7"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="17" t="s">
+      <c r="A132" s="15" t="s">
         <v>202</v>
       </c>
       <c r="B132" s="8" t="s">
@@ -8966,7 +8966,7 @@
       <c r="L133" s="7"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="17" t="s">
+      <c r="A134" s="15" t="s">
         <v>205</v>
       </c>
       <c r="B134" s="8" t="s">
@@ -9014,7 +9014,7 @@
       <c r="L135" s="7"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="17" t="s">
+      <c r="A136" s="15" t="s">
         <v>208</v>
       </c>
       <c r="B136" s="8"/>
@@ -9120,7 +9120,7 @@
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="15" t="s">
+      <c r="A143" s="17" t="s">
         <v>326</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -9168,7 +9168,7 @@
       <c r="L144" s="7"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
+      <c r="A145" s="15" t="s">
         <v>329</v>
       </c>
       <c r="B145" s="8" t="s">
@@ -9216,7 +9216,7 @@
       <c r="L146" s="7"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="17" t="s">
+      <c r="A147" s="15" t="s">
         <v>332</v>
       </c>
       <c r="B147" s="8" t="s">
@@ -9268,7 +9268,7 @@
       <c r="L148" s="7"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="17" t="s">
+      <c r="A149" s="15" t="s">
         <v>335</v>
       </c>
       <c r="B149" s="8" t="s">
@@ -9316,7 +9316,7 @@
       <c r="L150" s="7"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="17" t="s">
+      <c r="A151" s="15" t="s">
         <v>338</v>
       </c>
       <c r="B151" s="8" t="s">
@@ -9364,7 +9364,7 @@
       <c r="L152" s="7"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="17" t="s">
+      <c r="A153" s="15" t="s">
         <v>341</v>
       </c>
       <c r="B153" s="8" t="s">
@@ -9412,7 +9412,7 @@
       <c r="L154" s="7"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="17" t="s">
+      <c r="A155" s="15" t="s">
         <v>344</v>
       </c>
       <c r="B155" s="8" t="s">
@@ -9456,7 +9456,7 @@
       <c r="L156" s="7"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="17" t="s">
+      <c r="A157" s="15" t="s">
         <v>347</v>
       </c>
       <c r="B157" s="8" t="s">
@@ -9504,7 +9504,7 @@
       <c r="L158" s="7"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="17" t="s">
+      <c r="A159" s="15" t="s">
         <v>350</v>
       </c>
       <c r="B159" s="8" t="s">
@@ -9548,7 +9548,7 @@
       <c r="L160" s="7"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="17" t="s">
+      <c r="A161" s="15" t="s">
         <v>353</v>
       </c>
       <c r="B161" s="8" t="s">
@@ -9596,7 +9596,7 @@
       <c r="L162" s="7"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="17" t="s">
+      <c r="A163" s="15" t="s">
         <v>357</v>
       </c>
       <c r="B163" s="8" t="s">
@@ -9644,7 +9644,7 @@
       <c r="L164" s="7"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="17" t="s">
+      <c r="A165" s="15" t="s">
         <v>360</v>
       </c>
       <c r="B165" s="8" t="s">
@@ -9692,7 +9692,7 @@
       <c r="L166" s="7"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="17" t="s">
+      <c r="A167" s="15" t="s">
         <v>363</v>
       </c>
       <c r="B167" s="8" t="s">
@@ -9740,7 +9740,7 @@
       <c r="L168" s="7"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="17" t="s">
+      <c r="A169" s="15" t="s">
         <v>366</v>
       </c>
       <c r="B169" s="8" t="s">
@@ -9788,7 +9788,7 @@
       <c r="L170" s="7"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="17" t="s">
+      <c r="A171" s="15" t="s">
         <v>369</v>
       </c>
       <c r="B171" s="8" t="s">
@@ -9834,7 +9834,7 @@
       <c r="L172" s="7"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="17" t="s">
+      <c r="A173" s="15" t="s">
         <v>372</v>
       </c>
       <c r="B173" s="8" t="s">
@@ -9882,7 +9882,7 @@
       <c r="L174" s="7"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="17" t="s">
+      <c r="A175" s="15" t="s">
         <v>375</v>
       </c>
       <c r="B175" s="8" t="s">
@@ -9930,7 +9930,7 @@
       <c r="L176" s="7"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="17" t="s">
+      <c r="A177" s="15" t="s">
         <v>378</v>
       </c>
       <c r="B177" s="8" t="s">
@@ -9978,7 +9978,7 @@
       <c r="L178" s="7"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="17" t="s">
+      <c r="A179" s="15" t="s">
         <v>381</v>
       </c>
       <c r="B179" s="8" t="s">
@@ -10026,7 +10026,7 @@
       <c r="L180" s="7"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="17" t="s">
+      <c r="A181" s="15" t="s">
         <v>384</v>
       </c>
       <c r="B181" s="8" t="s">
@@ -10074,7 +10074,7 @@
       <c r="L182" s="7"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="17" t="s">
+      <c r="A183" s="15" t="s">
         <v>387</v>
       </c>
       <c r="B183" s="8" t="s">
@@ -10122,7 +10122,7 @@
       <c r="L184" s="7"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="17" t="s">
+      <c r="A185" s="15" t="s">
         <v>390</v>
       </c>
       <c r="B185" s="8" t="s">
@@ -10170,7 +10170,7 @@
       <c r="L186" s="7"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="17" t="s">
+      <c r="A187" s="15" t="s">
         <v>393</v>
       </c>
       <c r="B187" s="8" t="s">
@@ -10218,7 +10218,7 @@
       <c r="L188" s="7"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" s="17" t="s">
+      <c r="A189" s="15" t="s">
         <v>396</v>
       </c>
       <c r="B189" s="8" t="s">
@@ -10266,7 +10266,7 @@
       <c r="L190" s="7"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="17" t="s">
+      <c r="A191" s="15" t="s">
         <v>399</v>
       </c>
       <c r="B191" s="8" t="s">
@@ -10314,7 +10314,7 @@
       <c r="L192" s="7"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="17" t="s">
+      <c r="A193" s="15" t="s">
         <v>402</v>
       </c>
       <c r="B193" s="8" t="s">
@@ -10362,7 +10362,7 @@
       <c r="L194" s="7"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="17" t="s">
+      <c r="A195" s="15" t="s">
         <v>405</v>
       </c>
       <c r="B195" s="8" t="s">
@@ -10410,7 +10410,7 @@
       <c r="L196" s="7"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="17" t="s">
+      <c r="A197" s="15" t="s">
         <v>408</v>
       </c>
       <c r="B197" s="8" t="s">
@@ -10446,7 +10446,7 @@
       <c r="L198" s="7"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="17" t="s">
+      <c r="A199" s="15" t="s">
         <v>409</v>
       </c>
       <c r="B199" s="8" t="s">
@@ -10494,7 +10494,7 @@
       <c r="L200" s="7"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="17" t="s">
+      <c r="A201" s="15" t="s">
         <v>412</v>
       </c>
       <c r="B201" s="8"/>
@@ -10540,7 +10540,7 @@
       <c r="L202" s="7"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="17" t="s">
+      <c r="A203" s="15" t="s">
         <v>414</v>
       </c>
       <c r="B203" s="8" t="s">
@@ -10588,7 +10588,7 @@
       <c r="L204" s="7"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A205" s="17" t="s">
+      <c r="A205" s="15" t="s">
         <v>417</v>
       </c>
       <c r="B205" s="8" t="s">
@@ -10636,7 +10636,7 @@
       <c r="L206" s="7"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" s="17" t="s">
+      <c r="A207" s="15" t="s">
         <v>420</v>
       </c>
       <c r="B207" s="8" t="s">
@@ -10684,7 +10684,7 @@
       <c r="L208" s="7"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="17" t="s">
+      <c r="A209" s="15" t="s">
         <v>423</v>
       </c>
       <c r="B209" s="8"/>
@@ -10726,7 +10726,7 @@
       <c r="L210" s="7"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="17" t="s">
+      <c r="A211" s="15" t="s">
         <v>425</v>
       </c>
       <c r="B211" s="8" t="s">
@@ -10774,7 +10774,7 @@
       <c r="L212" s="7"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="17" t="s">
+      <c r="A213" s="15" t="s">
         <v>428</v>
       </c>
       <c r="B213" s="8" t="s">
@@ -10818,7 +10818,7 @@
       <c r="L214" s="7"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A215" s="17" t="s">
+      <c r="A215" s="15" t="s">
         <v>431</v>
       </c>
       <c r="B215" s="8" t="s">
@@ -10866,7 +10866,7 @@
       <c r="L216" s="7"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A217" s="17" t="s">
+      <c r="A217" s="15" t="s">
         <v>434</v>
       </c>
       <c r="B217" s="8" t="s">
@@ -10910,7 +10910,7 @@
       <c r="L218" s="7"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A219" s="17" t="s">
+      <c r="A219" s="15" t="s">
         <v>437</v>
       </c>
       <c r="B219" s="8" t="s">
@@ -10950,7 +10950,7 @@
       <c r="L220" s="7"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A221" s="17" t="s">
+      <c r="A221" s="15" t="s">
         <v>440</v>
       </c>
       <c r="B221" s="8"/>
@@ -10988,7 +10988,7 @@
       <c r="L222" s="7"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" s="17" t="s">
+      <c r="A223" s="15" t="s">
         <v>442</v>
       </c>
       <c r="B223" s="8"/>
@@ -11022,7 +11022,7 @@
       <c r="L224" s="7"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" s="17" t="s">
+      <c r="A225" s="15" t="s">
         <v>443</v>
       </c>
       <c r="B225" s="8" t="s">
@@ -11070,7 +11070,7 @@
       <c r="L226" s="7"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A227" s="17" t="s">
+      <c r="A227" s="15" t="s">
         <v>446</v>
       </c>
       <c r="B227" s="8"/>
@@ -11112,7 +11112,7 @@
       <c r="L228" s="7"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A229" s="17" t="s">
+      <c r="A229" s="15" t="s">
         <v>448</v>
       </c>
       <c r="B229" s="8" t="s">
@@ -11148,7 +11148,7 @@
       <c r="L230" s="7"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A231" s="17" t="s">
+      <c r="A231" s="15" t="s">
         <v>450</v>
       </c>
       <c r="B231" s="8" t="s">
@@ -11192,7 +11192,7 @@
       <c r="L232" s="7"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A233" s="17" t="s">
+      <c r="A233" s="15" t="s">
         <v>453</v>
       </c>
       <c r="B233" s="8" t="s">
@@ -11228,7 +11228,7 @@
       <c r="L234" s="7"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A235" s="17" t="s">
+      <c r="A235" s="15" t="s">
         <v>455</v>
       </c>
       <c r="B235" s="8"/>
@@ -11270,7 +11270,7 @@
       <c r="L236" s="7"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A237" s="17" t="s">
+      <c r="A237" s="15" t="s">
         <v>457</v>
       </c>
       <c r="B237" s="8" t="s">
@@ -11378,7 +11378,7 @@
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A244" s="15" t="s">
+      <c r="A244" s="17" t="s">
         <v>540</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -11426,7 +11426,7 @@
       <c r="L245" s="7"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A246" s="17" t="s">
+      <c r="A246" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B246" s="8" t="s">
@@ -11474,7 +11474,7 @@
       <c r="L247" s="7"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A248" s="17" t="s">
+      <c r="A248" s="15" t="s">
         <v>544</v>
       </c>
       <c r="B248" s="8" t="s">
@@ -11522,7 +11522,7 @@
       <c r="L249" s="7"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A250" s="17" t="s">
+      <c r="A250" s="15" t="s">
         <v>547</v>
       </c>
       <c r="B250" s="8" t="s">
@@ -11570,7 +11570,7 @@
       <c r="L251" s="7"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A252" s="17" t="s">
+      <c r="A252" s="15" t="s">
         <v>550</v>
       </c>
       <c r="B252" s="8" t="s">
@@ -11614,7 +11614,7 @@
       <c r="L253" s="7"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A254" s="17" t="s">
+      <c r="A254" s="15" t="s">
         <v>553</v>
       </c>
       <c r="B254" s="8" t="s">
@@ -11662,7 +11662,7 @@
       <c r="L255" s="7"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A256" s="17" t="s">
+      <c r="A256" s="15" t="s">
         <v>556</v>
       </c>
       <c r="B256" s="8" t="s">
@@ -11706,7 +11706,7 @@
       <c r="L257" s="7"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A258" s="17" t="s">
+      <c r="A258" s="15" t="s">
         <v>559</v>
       </c>
       <c r="B258" s="8" t="s">
@@ -11754,7 +11754,7 @@
       <c r="L259" s="7"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A260" s="17" t="s">
+      <c r="A260" s="15" t="s">
         <v>562</v>
       </c>
       <c r="B260" s="8" t="s">
@@ -11802,7 +11802,7 @@
       <c r="L261" s="7"/>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A262" s="17" t="s">
+      <c r="A262" s="15" t="s">
         <v>565</v>
       </c>
       <c r="B262" s="8" t="s">
@@ -11850,7 +11850,7 @@
       <c r="L263" s="7"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A264" s="17" t="s">
+      <c r="A264" s="15" t="s">
         <v>568</v>
       </c>
       <c r="B264" s="8" t="s">
@@ -11898,7 +11898,7 @@
       <c r="L265" s="7"/>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" s="17" t="s">
+      <c r="A266" s="15" t="s">
         <v>571</v>
       </c>
       <c r="B266" s="8" t="s">
@@ -11946,7 +11946,7 @@
       <c r="L267" s="7"/>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A268" s="17" t="s">
+      <c r="A268" s="15" t="s">
         <v>574</v>
       </c>
       <c r="B268" s="8" t="s">
@@ -11986,7 +11986,7 @@
       <c r="L269" s="7"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A270" s="17" t="s">
+      <c r="A270" s="15" t="s">
         <v>577</v>
       </c>
       <c r="B270" s="8" t="s">
@@ -12034,7 +12034,7 @@
       <c r="L271" s="7"/>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A272" s="17" t="s">
+      <c r="A272" s="15" t="s">
         <v>579</v>
       </c>
       <c r="B272" s="8" t="s">
@@ -12082,7 +12082,7 @@
       <c r="L273" s="7"/>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A274" s="17" t="s">
+      <c r="A274" s="15" t="s">
         <v>582</v>
       </c>
       <c r="B274" s="8" t="s">
@@ -12134,7 +12134,7 @@
       <c r="L275" s="7"/>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A276" s="17" t="s">
+      <c r="A276" s="15" t="s">
         <v>585</v>
       </c>
       <c r="B276" s="8" t="s">
@@ -12178,7 +12178,7 @@
       <c r="L277" s="7"/>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A278" s="17" t="s">
+      <c r="A278" s="15" t="s">
         <v>588</v>
       </c>
       <c r="B278" s="8" t="s">
@@ -12226,7 +12226,7 @@
       <c r="L279" s="7"/>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A280" s="17" t="s">
+      <c r="A280" s="15" t="s">
         <v>590</v>
       </c>
       <c r="B280" s="8" t="s">
@@ -12274,7 +12274,7 @@
       <c r="L281" s="7"/>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A282" s="17" t="s">
+      <c r="A282" s="15" t="s">
         <v>593</v>
       </c>
       <c r="B282" s="8" t="s">
@@ -12322,7 +12322,7 @@
       <c r="L283" s="7"/>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A284" s="17" t="s">
+      <c r="A284" s="15" t="s">
         <v>596</v>
       </c>
       <c r="B284" s="8" t="s">
@@ -12370,7 +12370,7 @@
       <c r="L285" s="7"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A286" s="17" t="s">
+      <c r="A286" s="15" t="s">
         <v>599</v>
       </c>
       <c r="B286" s="8"/>
@@ -12412,7 +12412,7 @@
       <c r="L287" s="7"/>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A288" s="17" t="s">
+      <c r="A288" s="15" t="s">
         <v>601</v>
       </c>
       <c r="B288" s="8" t="s">
@@ -12456,7 +12456,7 @@
       <c r="L289" s="7"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A290" s="17" t="s">
+      <c r="A290" s="15" t="s">
         <v>604</v>
       </c>
       <c r="B290" s="8"/>
@@ -12502,7 +12502,7 @@
       <c r="L291" s="7"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A292" s="17" t="s">
+      <c r="A292" s="15" t="s">
         <v>606</v>
       </c>
       <c r="B292" s="8"/>
@@ -12548,7 +12548,7 @@
       <c r="L293" s="7"/>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A294" s="17" t="s">
+      <c r="A294" s="15" t="s">
         <v>608</v>
       </c>
       <c r="B294" s="8"/>
@@ -12594,7 +12594,7 @@
       <c r="L295" s="7"/>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A296" s="17" t="s">
+      <c r="A296" s="15" t="s">
         <v>610</v>
       </c>
       <c r="B296" s="8" t="s">
@@ -12642,7 +12642,7 @@
       <c r="L297" s="7"/>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A298" s="17" t="s">
+      <c r="A298" s="15" t="s">
         <v>613</v>
       </c>
       <c r="B298" s="8" t="s">
@@ -12690,7 +12690,7 @@
       <c r="L299" s="7"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A300" s="17" t="s">
+      <c r="A300" s="15" t="s">
         <v>616</v>
       </c>
       <c r="B300" s="8" t="s">
@@ -12738,7 +12738,7 @@
       <c r="L301" s="7"/>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A302" s="17" t="s">
+      <c r="A302" s="15" t="s">
         <v>619</v>
       </c>
       <c r="B302" s="8" t="s">
@@ -12782,7 +12782,7 @@
       <c r="L303" s="7"/>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A304" s="17" t="s">
+      <c r="A304" s="15" t="s">
         <v>622</v>
       </c>
       <c r="B304" s="8" t="s">
@@ -12822,7 +12822,7 @@
       <c r="L305" s="7"/>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A306" s="17" t="s">
+      <c r="A306" s="15" t="s">
         <v>625</v>
       </c>
       <c r="B306" s="8" t="s">
@@ -12870,7 +12870,7 @@
       <c r="L307" s="7"/>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A308" s="17" t="s">
+      <c r="A308" s="15" t="s">
         <v>628</v>
       </c>
       <c r="B308" s="8" t="s">
@@ -12918,7 +12918,7 @@
       <c r="L309" s="7"/>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A310" s="17" t="s">
+      <c r="A310" s="15" t="s">
         <v>631</v>
       </c>
       <c r="B310" s="8" t="s">
@@ -12966,7 +12966,7 @@
       <c r="L311" s="7"/>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A312" s="17" t="s">
+      <c r="A312" s="15" t="s">
         <v>634</v>
       </c>
       <c r="B312" s="8" t="s">
@@ -13010,7 +13010,7 @@
       <c r="L313" s="7"/>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A314" s="17" t="s">
+      <c r="A314" s="15" t="s">
         <v>637</v>
       </c>
       <c r="B314" s="8" t="s">
@@ -13058,7 +13058,7 @@
       <c r="L315" s="7"/>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A316" s="17" t="s">
+      <c r="A316" s="15" t="s">
         <v>640</v>
       </c>
       <c r="B316" s="8" t="s">
@@ -13094,7 +13094,7 @@
       <c r="L317" s="7"/>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A318" s="17" t="s">
+      <c r="A318" s="15" t="s">
         <v>642</v>
       </c>
       <c r="B318" s="8" t="s">
@@ -13138,7 +13138,7 @@
       <c r="L319" s="7"/>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A320" s="17" t="s">
+      <c r="A320" s="15" t="s">
         <v>645</v>
       </c>
       <c r="B320" s="8" t="s">
@@ -13182,7 +13182,7 @@
       <c r="L321" s="7"/>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A322" s="17" t="s">
+      <c r="A322" s="15" t="s">
         <v>648</v>
       </c>
       <c r="B322" s="8" t="s">
@@ -13226,7 +13226,7 @@
       <c r="L323" s="7"/>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A324" s="17" t="s">
+      <c r="A324" s="15" t="s">
         <v>651</v>
       </c>
       <c r="B324" s="8" t="s">
@@ -13274,7 +13274,7 @@
       <c r="L325" s="7"/>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A326" s="17" t="s">
+      <c r="A326" s="15" t="s">
         <v>654</v>
       </c>
       <c r="B326" s="8" t="s">
@@ -13322,7 +13322,7 @@
       <c r="L327" s="7"/>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A328" s="17" t="s">
+      <c r="A328" s="15" t="s">
         <v>657</v>
       </c>
       <c r="B328" s="8" t="s">
@@ -13366,7 +13366,7 @@
       <c r="L329" s="7"/>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A330" s="17" t="s">
+      <c r="A330" s="15" t="s">
         <v>660</v>
       </c>
       <c r="B330" s="8" t="s">
@@ -13406,7 +13406,7 @@
       <c r="L331" s="7"/>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A332" s="17" t="s">
+      <c r="A332" s="15" t="s">
         <v>663</v>
       </c>
       <c r="B332" s="8" t="s">
@@ -13454,7 +13454,7 @@
       <c r="L333" s="7"/>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A334" s="17" t="s">
+      <c r="A334" s="15" t="s">
         <v>666</v>
       </c>
       <c r="B334" s="8" t="s">
@@ -13494,7 +13494,7 @@
       <c r="L335" s="7"/>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A336" s="17" t="s">
+      <c r="A336" s="15" t="s">
         <v>668</v>
       </c>
       <c r="B336" s="8" t="s">
@@ -13538,7 +13538,7 @@
       <c r="L337" s="7"/>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A338" s="17" t="s">
+      <c r="A338" s="15" t="s">
         <v>671</v>
       </c>
       <c r="B338" s="8" t="s">
@@ -13574,7 +13574,7 @@
       <c r="L339" s="7"/>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A340" s="17" t="s">
+      <c r="A340" s="15" t="s">
         <v>673</v>
       </c>
       <c r="B340" s="8" t="s">
@@ -13614,7 +13614,7 @@
       <c r="L341" s="7"/>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A342" s="17" t="s">
+      <c r="A342" s="15" t="s">
         <v>676</v>
       </c>
       <c r="B342" s="8" t="s">
@@ -13650,7 +13650,7 @@
       <c r="L343" s="7"/>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A344" s="17" t="s">
+      <c r="A344" s="15" t="s">
         <v>678</v>
       </c>
       <c r="B344" s="8" t="s">
@@ -13698,7 +13698,7 @@
       <c r="L345" s="7"/>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A346" s="17" t="s">
+      <c r="A346" s="15" t="s">
         <v>681</v>
       </c>
       <c r="B346" s="8" t="s">
@@ -13742,7 +13742,7 @@
       <c r="L347" s="7"/>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A348" s="17" t="s">
+      <c r="A348" s="15" t="s">
         <v>684</v>
       </c>
       <c r="B348" s="8" t="s">
@@ -13790,7 +13790,7 @@
       <c r="L349" s="7"/>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A350" s="17" t="s">
+      <c r="A350" s="15" t="s">
         <v>687</v>
       </c>
       <c r="B350" s="8"/>
@@ -13828,7 +13828,7 @@
       <c r="L351" s="7"/>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A352" s="17" t="s">
+      <c r="A352" s="15" t="s">
         <v>689</v>
       </c>
       <c r="B352" s="8"/>
@@ -13862,7 +13862,7 @@
       <c r="L353" s="7"/>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A354" s="17" t="s">
+      <c r="A354" s="15" t="s">
         <v>690</v>
       </c>
       <c r="B354" s="8"/>
@@ -13900,7 +13900,7 @@
       <c r="L355" s="7"/>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A356" s="17" t="s">
+      <c r="A356" s="15" t="s">
         <v>692</v>
       </c>
       <c r="B356" s="8"/>
@@ -13942,7 +13942,7 @@
       <c r="L357" s="7"/>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A358" s="17" t="s">
+      <c r="A358" s="15" t="s">
         <v>666</v>
       </c>
       <c r="B358" s="8"/>
@@ -13976,7 +13976,7 @@
       <c r="L359" s="7"/>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A360" s="17" t="s">
+      <c r="A360" s="15" t="s">
         <v>694</v>
       </c>
       <c r="B360" s="8"/>
@@ -14067,7 +14067,7 @@
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A367" s="15" t="s">
+      <c r="A367" s="17" t="s">
         <v>45</v>
       </c>
       <c r="B367" s="2" t="s">
@@ -14101,7 +14101,7 @@
       <c r="I368" s="7"/>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A369" s="17" t="s">
+      <c r="A369" s="15" t="s">
         <v>780</v>
       </c>
       <c r="B369" s="8" t="s">
@@ -14135,7 +14135,7 @@
       <c r="I370" s="7"/>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A371" s="17" t="s">
+      <c r="A371" s="15" t="s">
         <v>784</v>
       </c>
       <c r="B371" s="8" t="s">
@@ -14165,7 +14165,7 @@
       <c r="I372" s="7"/>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A373" s="17" t="s">
+      <c r="A373" s="15" t="s">
         <v>786</v>
       </c>
       <c r="B373" s="8" t="s">
@@ -14199,7 +14199,7 @@
       <c r="I374" s="7"/>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A375" s="17" t="s">
+      <c r="A375" s="15" t="s">
         <v>789</v>
       </c>
       <c r="B375" s="8" t="s">
@@ -14233,7 +14233,7 @@
       <c r="I376" s="7"/>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A377" s="17" t="s">
+      <c r="A377" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B377" s="8" t="s">
@@ -14267,7 +14267,7 @@
       <c r="I378" s="7"/>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A379" s="17" t="s">
+      <c r="A379" s="15" t="s">
         <v>793</v>
       </c>
       <c r="B379" s="8"/>
@@ -14299,7 +14299,7 @@
       <c r="I380" s="7"/>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A381" s="17" t="s">
+      <c r="A381" s="15" t="s">
         <v>794</v>
       </c>
       <c r="B381" s="8" t="s">
@@ -14333,7 +14333,7 @@
       <c r="I382" s="7"/>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A383" s="17" t="s">
+      <c r="A383" s="15" t="s">
         <v>797</v>
       </c>
       <c r="B383" s="8"/>
@@ -14361,7 +14361,7 @@
       <c r="I384" s="7"/>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A385" s="17" t="s">
+      <c r="A385" s="15" t="s">
         <v>800</v>
       </c>
       <c r="B385" s="8" t="s">
@@ -14391,7 +14391,7 @@
       <c r="I386" s="7"/>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A387" s="17" t="s">
+      <c r="A387" s="15" t="s">
         <v>803</v>
       </c>
       <c r="B387" s="8"/>
@@ -14419,7 +14419,7 @@
       <c r="I388" s="7"/>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A389" s="17" t="s">
+      <c r="A389" s="15" t="s">
         <v>805</v>
       </c>
       <c r="B389" s="8"/>
@@ -14451,7 +14451,7 @@
       <c r="I390" s="7"/>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A391" s="17" t="s">
+      <c r="A391" s="15" t="s">
         <v>660</v>
       </c>
       <c r="B391" s="8" t="s">
@@ -14485,7 +14485,7 @@
       <c r="I392" s="7"/>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A393" s="17" t="s">
+      <c r="A393" s="15" t="s">
         <v>809</v>
       </c>
       <c r="B393" s="8" t="s">
@@ -14519,7 +14519,7 @@
       <c r="I394" s="7"/>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A395" s="17" t="s">
+      <c r="A395" s="15" t="s">
         <v>812</v>
       </c>
       <c r="B395" s="8" t="s">
@@ -14549,7 +14549,7 @@
       <c r="I396" s="7"/>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A397" s="17" t="s">
+      <c r="A397" s="15" t="s">
         <v>815</v>
       </c>
       <c r="B397" s="8" t="s">
@@ -14579,7 +14579,7 @@
       <c r="I398" s="7"/>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A399" s="17" t="s">
+      <c r="A399" s="15" t="s">
         <v>645</v>
       </c>
       <c r="B399" s="8">
@@ -14613,7 +14613,7 @@
       <c r="I400" s="7"/>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A401" s="17" t="s">
+      <c r="A401" s="15" t="s">
         <v>820</v>
       </c>
       <c r="B401" s="8" t="s">
@@ -14647,7 +14647,7 @@
       <c r="I402" s="7"/>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A403" s="17" t="s">
+      <c r="A403" s="15" t="s">
         <v>823</v>
       </c>
       <c r="B403" s="8" t="s">
@@ -14681,7 +14681,7 @@
       <c r="I404" s="7"/>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A405" s="17" t="s">
+      <c r="A405" s="15" t="s">
         <v>826</v>
       </c>
       <c r="B405" s="8" t="s">
@@ -14715,7 +14715,7 @@
       <c r="I406" s="7"/>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A407" s="17" t="s">
+      <c r="A407" s="15" t="s">
         <v>831</v>
       </c>
       <c r="B407" s="8"/>
@@ -14747,7 +14747,7 @@
       <c r="I408" s="7"/>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A409" s="17" t="s">
+      <c r="A409" s="15" t="s">
         <v>360</v>
       </c>
       <c r="B409" s="8" t="s">
@@ -14781,7 +14781,7 @@
       <c r="I410" s="7"/>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A411" s="17" t="s">
+      <c r="A411" s="15" t="s">
         <v>835</v>
       </c>
       <c r="B411" s="8"/>
@@ -14813,7 +14813,7 @@
       <c r="I412" s="7"/>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A413" s="17" t="s">
+      <c r="A413" s="15" t="s">
         <v>837</v>
       </c>
       <c r="B413" s="8"/>
@@ -14845,7 +14845,7 @@
       <c r="I414" s="7"/>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A415" s="17" t="s">
+      <c r="A415" s="15" t="s">
         <v>839</v>
       </c>
       <c r="B415" s="8"/>
@@ -14877,7 +14877,7 @@
       <c r="I416" s="7"/>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A417" s="17" t="s">
+      <c r="A417" s="15" t="s">
         <v>841</v>
       </c>
       <c r="B417" s="8"/>
@@ -14905,7 +14905,7 @@
       <c r="I418" s="7"/>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A419" s="17" t="s">
+      <c r="A419" s="15" t="s">
         <v>544</v>
       </c>
       <c r="B419" s="8"/>
@@ -14937,7 +14937,7 @@
       <c r="I420" s="7"/>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A421" s="17" t="s">
+      <c r="A421" s="15" t="s">
         <v>844</v>
       </c>
       <c r="B421" s="8"/>
@@ -14969,7 +14969,7 @@
       <c r="I422" s="7"/>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A423" s="17" t="s">
+      <c r="A423" s="15" t="s">
         <v>547</v>
       </c>
       <c r="B423" s="8"/>
@@ -15001,7 +15001,7 @@
       <c r="I424" s="7"/>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A425" s="17" t="s">
+      <c r="A425" s="15" t="s">
         <v>847</v>
       </c>
       <c r="B425" s="8"/>
@@ -15031,7 +15031,7 @@
       <c r="I426" s="7"/>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A427" s="17" t="s">
+      <c r="A427" s="15" t="s">
         <v>849</v>
       </c>
       <c r="B427" s="8"/>
@@ -15063,7 +15063,7 @@
       <c r="I428" s="7"/>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A429" s="17" t="s">
+      <c r="A429" s="15" t="s">
         <v>851</v>
       </c>
       <c r="B429" s="8"/>
@@ -15095,7 +15095,7 @@
       <c r="I430" s="7"/>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A431" s="17" t="s">
+      <c r="A431" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B431" s="8"/>
@@ -15123,7 +15123,7 @@
       <c r="I432" s="7"/>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A433" s="17" t="s">
+      <c r="A433" s="15" t="s">
         <v>854</v>
       </c>
       <c r="B433" s="8"/>
@@ -15155,7 +15155,7 @@
       <c r="I434" s="7"/>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A435" s="17" t="s">
+      <c r="A435" s="15" t="s">
         <v>856</v>
       </c>
       <c r="B435" s="8"/>
@@ -15187,7 +15187,7 @@
       <c r="I436" s="7"/>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A437" s="17" t="s">
+      <c r="A437" s="15" t="s">
         <v>113</v>
       </c>
       <c r="B437" s="8" t="s">
@@ -15270,7 +15270,7 @@
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A444" s="15" t="s">
+      <c r="A444" s="17" t="s">
         <v>859</v>
       </c>
       <c r="B444" s="2" t="s">
@@ -15308,7 +15308,7 @@
       <c r="I445" s="7"/>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A446" s="17" t="s">
+      <c r="A446" s="15" t="s">
         <v>864</v>
       </c>
       <c r="B446" s="8" t="s">
@@ -15346,7 +15346,7 @@
       <c r="I447" s="7"/>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A448" s="17" t="s">
+      <c r="A448" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B448" s="8" t="s">
@@ -15380,7 +15380,7 @@
       <c r="I449" s="7"/>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A450" s="17" t="s">
+      <c r="A450" s="15" t="s">
         <v>809</v>
       </c>
       <c r="B450" s="8" t="s">
@@ -15418,7 +15418,7 @@
       <c r="I451" s="7"/>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A452" s="17" t="s">
+      <c r="A452" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B452" s="8" t="s">
@@ -15452,7 +15452,7 @@
       <c r="I453" s="7"/>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A454" s="17" t="s">
+      <c r="A454" s="15" t="s">
         <v>104</v>
       </c>
       <c r="B454" s="8" t="s">
@@ -15486,7 +15486,7 @@
       <c r="I455" s="7"/>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A456" s="17" t="s">
+      <c r="A456" s="15" t="s">
         <v>353</v>
       </c>
       <c r="B456" s="8" t="s">
@@ -15524,7 +15524,7 @@
       <c r="I457" s="7"/>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A458" s="17" t="s">
+      <c r="A458" s="15" t="s">
         <v>879</v>
       </c>
       <c r="B458" s="8" t="s">
@@ -15562,7 +15562,7 @@
       <c r="I459" s="7"/>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A460" s="17" t="s">
+      <c r="A460" s="15" t="s">
         <v>805</v>
       </c>
       <c r="B460" s="8" t="s">
@@ -15596,7 +15596,7 @@
       <c r="I461" s="7"/>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A462" s="17" t="s">
+      <c r="A462" s="15" t="s">
         <v>885</v>
       </c>
       <c r="B462" s="8" t="s">
@@ -15634,7 +15634,7 @@
       <c r="I463" s="7"/>
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A464" s="17" t="s">
+      <c r="A464" s="15" t="s">
         <v>890</v>
       </c>
       <c r="B464" s="8" t="s">
@@ -15668,7 +15668,7 @@
       <c r="I465" s="7"/>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A466" s="17" t="s">
+      <c r="A466" s="15" t="s">
         <v>893</v>
       </c>
       <c r="B466" s="8" t="s">
@@ -15702,7 +15702,7 @@
       <c r="I467" s="7"/>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A468" s="17" t="s">
+      <c r="A468" s="15" t="s">
         <v>896</v>
       </c>
       <c r="B468" s="8" t="s">
@@ -15732,7 +15732,7 @@
       <c r="I469" s="7"/>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A470" s="17" t="s">
+      <c r="A470" s="15" t="s">
         <v>899</v>
       </c>
       <c r="B470" s="8" t="s">
@@ -15766,7 +15766,7 @@
       <c r="I471" s="7"/>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A472" s="17" t="s">
+      <c r="A472" s="15" t="s">
         <v>902</v>
       </c>
       <c r="B472" s="8" t="s">
@@ -15800,7 +15800,7 @@
       <c r="I473" s="7"/>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A474" s="17" t="s">
+      <c r="A474" s="15" t="s">
         <v>905</v>
       </c>
       <c r="B474" s="8"/>
@@ -15832,7 +15832,7 @@
       <c r="I475" s="7"/>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A476" s="17" t="s">
+      <c r="A476" s="15" t="s">
         <v>907</v>
       </c>
       <c r="B476" s="8" t="s">
@@ -15870,7 +15870,7 @@
       <c r="I477" s="7"/>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A478" s="17" t="s">
+      <c r="A478" s="15" t="s">
         <v>912</v>
       </c>
       <c r="B478" s="8"/>
@@ -15902,7 +15902,7 @@
       <c r="I479" s="7"/>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A480" s="17" t="s">
+      <c r="A480" s="15" t="s">
         <v>913</v>
       </c>
       <c r="B480" s="8" t="s">
@@ -15932,7 +15932,7 @@
       <c r="I481" s="7"/>
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A482" s="17" t="s">
+      <c r="A482" s="15" t="s">
         <v>916</v>
       </c>
       <c r="B482" s="8" t="s">
@@ -15966,7 +15966,7 @@
       <c r="I483" s="7"/>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A484" s="17" t="s">
+      <c r="A484" s="15" t="s">
         <v>919</v>
       </c>
       <c r="B484" s="8"/>
@@ -16002,7 +16002,7 @@
       <c r="I485" s="7"/>
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A486" s="17" t="s">
+      <c r="A486" s="15" t="s">
         <v>922</v>
       </c>
       <c r="B486" s="8"/>
@@ -16038,7 +16038,7 @@
       <c r="I487" s="7"/>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A488" s="17" t="s">
+      <c r="A488" s="15" t="s">
         <v>186</v>
       </c>
       <c r="B488" s="8"/>
@@ -16070,7 +16070,7 @@
       <c r="I489" s="7"/>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A490" s="17" t="s">
+      <c r="A490" s="15" t="s">
         <v>926</v>
       </c>
       <c r="B490" s="8"/>
@@ -16106,7 +16106,7 @@
       <c r="I491" s="7"/>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A492" s="17" t="s">
+      <c r="A492" s="15" t="s">
         <v>929</v>
       </c>
       <c r="B492" s="8"/>
@@ -16142,7 +16142,7 @@
       <c r="I493" s="7"/>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A494" s="17" t="s">
+      <c r="A494" s="15" t="s">
         <v>932</v>
       </c>
       <c r="B494" s="8"/>
@@ -16174,7 +16174,7 @@
       <c r="I495" s="7"/>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A496" s="17" t="s">
+      <c r="A496" s="15" t="s">
         <v>896</v>
       </c>
       <c r="B496" s="8"/>
@@ -16202,7 +16202,7 @@
       <c r="I497" s="7"/>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A498" s="17" t="s">
+      <c r="A498" s="15" t="s">
         <v>935</v>
       </c>
       <c r="B498" s="8"/>
@@ -16234,7 +16234,7 @@
       <c r="I499" s="7"/>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A500" s="17" t="s">
+      <c r="A500" s="15" t="s">
         <v>937</v>
       </c>
       <c r="B500" s="8"/>
@@ -16266,7 +16266,7 @@
       <c r="I501" s="7"/>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A502" s="17" t="s">
+      <c r="A502" s="15" t="s">
         <v>939</v>
       </c>
       <c r="B502" s="8"/>
@@ -16298,7 +16298,7 @@
       <c r="I503" s="7"/>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A504" s="17" t="s">
+      <c r="A504" s="15" t="s">
         <v>941</v>
       </c>
       <c r="B504" s="8"/>
@@ -16330,7 +16330,7 @@
       <c r="I505" s="7"/>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A506" s="17" t="s">
+      <c r="A506" s="15" t="s">
         <v>945</v>
       </c>
       <c r="B506" s="8"/>
@@ -16362,7 +16362,7 @@
       <c r="I507" s="7"/>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A508" s="17" t="s">
+      <c r="A508" s="15" t="s">
         <v>947</v>
       </c>
       <c r="B508" s="8"/>
@@ -16394,7 +16394,7 @@
       <c r="I509" s="7"/>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A510" s="17" t="s">
+      <c r="A510" s="15" t="s">
         <v>160</v>
       </c>
       <c r="B510" s="8"/>
@@ -16426,7 +16426,7 @@
       <c r="I511" s="7"/>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A512" s="17" t="s">
+      <c r="A512" s="15" t="s">
         <v>949</v>
       </c>
       <c r="B512" s="8" t="s">
@@ -16460,7 +16460,7 @@
       <c r="I513" s="7"/>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A514" s="17" t="s">
+      <c r="A514" s="15" t="s">
         <v>952</v>
       </c>
       <c r="B514" s="8" t="s">
@@ -16498,7 +16498,7 @@
       <c r="I515" s="7"/>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A516" s="17" t="s">
+      <c r="A516" s="15" t="s">
         <v>956</v>
       </c>
       <c r="B516" s="8" t="s">
@@ -16528,7 +16528,7 @@
       <c r="I517" s="7"/>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A518" s="17" t="s">
+      <c r="A518" s="15" t="s">
         <v>420</v>
       </c>
       <c r="B518" s="8"/>
@@ -16560,7 +16560,7 @@
       <c r="I519" s="7"/>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A520" s="17" t="s">
+      <c r="A520" s="15" t="s">
         <v>960</v>
       </c>
       <c r="B520" s="8"/>
@@ -16592,7 +16592,7 @@
       <c r="I521" s="7"/>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A522" s="17" t="s">
+      <c r="A522" s="15" t="s">
         <v>645</v>
       </c>
       <c r="B522" s="8"/>
@@ -16673,7 +16673,7 @@
       </c>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A529" s="15" t="s">
+      <c r="A529" s="17" t="s">
         <v>964</v>
       </c>
       <c r="B529" s="2" t="s">
@@ -16703,7 +16703,7 @@
       <c r="I530" s="7"/>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A531" s="17" t="s">
+      <c r="A531" s="15" t="s">
         <v>967</v>
       </c>
       <c r="B531" s="8" t="s">
@@ -16737,7 +16737,7 @@
       <c r="I532" s="7"/>
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A533" s="17" t="s">
+      <c r="A533" s="15" t="s">
         <v>970</v>
       </c>
       <c r="B533" s="8" t="s">
@@ -16771,7 +16771,7 @@
       <c r="I534" s="7"/>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A535" s="17" t="s">
+      <c r="A535" s="15" t="s">
         <v>973</v>
       </c>
       <c r="B535" s="8" t="s">
@@ -16805,7 +16805,7 @@
       <c r="I536" s="7"/>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A537" s="17" t="s">
+      <c r="A537" s="15" t="s">
         <v>977</v>
       </c>
       <c r="B537" s="8" t="s">
@@ -16839,7 +16839,7 @@
       <c r="I538" s="7"/>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A539" s="17" t="s">
+      <c r="A539" s="15" t="s">
         <v>980</v>
       </c>
       <c r="B539" s="8" t="s">
@@ -16873,7 +16873,7 @@
       <c r="I540" s="7"/>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A541" s="17" t="s">
+      <c r="A541" s="15" t="s">
         <v>983</v>
       </c>
       <c r="B541" s="8" t="s">
@@ -16907,7 +16907,7 @@
       <c r="I542" s="7"/>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A543" s="17" t="s">
+      <c r="A543" s="15" t="s">
         <v>986</v>
       </c>
       <c r="B543" s="8" t="s">
@@ -16941,7 +16941,7 @@
       <c r="I544" s="7"/>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A545" s="17" t="s">
+      <c r="A545" s="15" t="s">
         <v>990</v>
       </c>
       <c r="B545" s="8" t="s">
@@ -16975,7 +16975,7 @@
       <c r="I546" s="7"/>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A547" s="17" t="s">
+      <c r="A547" s="15" t="s">
         <v>993</v>
       </c>
       <c r="B547" s="8" t="s">
@@ -17009,7 +17009,7 @@
       <c r="I548" s="7"/>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A549" s="17" t="s">
+      <c r="A549" s="15" t="s">
         <v>996</v>
       </c>
       <c r="B549" s="8" t="s">
@@ -17043,7 +17043,7 @@
       <c r="I550" s="7"/>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A551" s="17" t="s">
+      <c r="A551" s="15" t="s">
         <v>1000</v>
       </c>
       <c r="B551" s="8" t="s">
@@ -17077,7 +17077,7 @@
       <c r="I552" s="7"/>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A553" s="17" t="s">
+      <c r="A553" s="15" t="s">
         <v>1004</v>
       </c>
       <c r="B553" s="8" t="s">
@@ -17111,7 +17111,7 @@
       <c r="I554" s="7"/>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A555" s="17" t="s">
+      <c r="A555" s="15" t="s">
         <v>1007</v>
       </c>
       <c r="B555" s="8" t="s">
@@ -17145,7 +17145,7 @@
       <c r="I556" s="7"/>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A557" s="17" t="s">
+      <c r="A557" s="15" t="s">
         <v>1010</v>
       </c>
       <c r="B557" s="8"/>
@@ -17177,7 +17177,7 @@
       <c r="I558" s="7"/>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A559" s="17" t="s">
+      <c r="A559" s="15" t="s">
         <v>1012</v>
       </c>
       <c r="B559" s="8" t="s">
@@ -17211,7 +17211,7 @@
       <c r="I560" s="7"/>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A561" s="17" t="s">
+      <c r="A561" s="15" t="s">
         <v>1016</v>
       </c>
       <c r="B561" s="8" t="s">
@@ -17245,7 +17245,7 @@
       <c r="I562" s="7"/>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A563" s="17" t="s">
+      <c r="A563" s="15" t="s">
         <v>1019</v>
       </c>
       <c r="B563" s="8" t="s">
@@ -17275,7 +17275,7 @@
       <c r="I564" s="7"/>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A565" s="17" t="s">
+      <c r="A565" s="15" t="s">
         <v>1022</v>
       </c>
       <c r="B565" s="8" t="s">
@@ -17309,7 +17309,7 @@
       <c r="I566" s="7"/>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A567" s="17" t="s">
+      <c r="A567" s="15" t="s">
         <v>1026</v>
       </c>
       <c r="B567" s="8" t="s">
@@ -17343,7 +17343,7 @@
       <c r="I568" s="7"/>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A569" s="17" t="s">
+      <c r="A569" s="15" t="s">
         <v>1029</v>
       </c>
       <c r="B569" s="8" t="s">
@@ -17377,7 +17377,7 @@
       <c r="I570" s="7"/>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A571" s="17" t="s">
+      <c r="A571" s="15" t="s">
         <v>1033</v>
       </c>
       <c r="B571" s="8" t="s">
@@ -17411,7 +17411,7 @@
       <c r="I572" s="7"/>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A573" s="17" t="s">
+      <c r="A573" s="15" t="s">
         <v>1036</v>
       </c>
       <c r="B573" s="8" t="s">
@@ -17445,7 +17445,7 @@
       <c r="I574" s="7"/>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A575" s="17" t="s">
+      <c r="A575" s="15" t="s">
         <v>1039</v>
       </c>
       <c r="B575" s="8"/>
@@ -17473,7 +17473,7 @@
       <c r="I576" s="7"/>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A577" s="17" t="s">
+      <c r="A577" s="15" t="s">
         <v>1041</v>
       </c>
       <c r="B577" s="8"/>
@@ -17501,7 +17501,7 @@
       <c r="I578" s="7"/>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A579" s="17" t="s">
+      <c r="A579" s="15" t="s">
         <v>1043</v>
       </c>
       <c r="B579" s="8" t="s">
@@ -17535,7 +17535,7 @@
       <c r="I580" s="7"/>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A581" s="17" t="s">
+      <c r="A581" s="15" t="s">
         <v>1047</v>
       </c>
       <c r="B581" s="8"/>
@@ -17567,7 +17567,7 @@
       <c r="I582" s="7"/>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A583" s="17" t="s">
+      <c r="A583" s="15" t="s">
         <v>1050</v>
       </c>
       <c r="B583" s="8" t="s">
@@ -17601,7 +17601,7 @@
       <c r="I584" s="7"/>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A585" s="17" t="s">
+      <c r="A585" s="15" t="s">
         <v>1054</v>
       </c>
       <c r="B585" s="8" t="s">
@@ -17635,7 +17635,7 @@
       <c r="I586" s="7"/>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A587" s="17" t="s">
+      <c r="A587" s="15" t="s">
         <v>1057</v>
       </c>
       <c r="B587" s="8"/>
@@ -17667,7 +17667,7 @@
       <c r="I588" s="7"/>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A589" s="17" t="s">
+      <c r="A589" s="15" t="s">
         <v>1059</v>
       </c>
       <c r="B589" s="8" t="s">
@@ -17701,7 +17701,7 @@
       <c r="I590" s="7"/>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A591" s="17" t="s">
+      <c r="A591" s="15" t="s">
         <v>1063</v>
       </c>
       <c r="B591" s="8" t="s">
@@ -17735,7 +17735,7 @@
       <c r="I592" s="7"/>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A593" s="17" t="s">
+      <c r="A593" s="15" t="s">
         <v>1067</v>
       </c>
       <c r="B593" s="8"/>
@@ -17767,7 +17767,7 @@
       <c r="I594" s="7"/>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A595" s="17" t="s">
+      <c r="A595" s="15" t="s">
         <v>1069</v>
       </c>
       <c r="B595" s="8"/>
@@ -17799,7 +17799,7 @@
       <c r="I596" s="7"/>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A597" s="17" t="s">
+      <c r="A597" s="15" t="s">
         <v>1071</v>
       </c>
       <c r="B597" s="8" t="s">
@@ -17833,7 +17833,7 @@
       <c r="I598" s="7"/>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A599" s="17" t="s">
+      <c r="A599" s="15" t="s">
         <v>1074</v>
       </c>
       <c r="B599" s="8" t="s">
@@ -17867,7 +17867,7 @@
       <c r="I600" s="7"/>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A601" s="17" t="s">
+      <c r="A601" s="15" t="s">
         <v>1078</v>
       </c>
       <c r="B601" s="8" t="s">
@@ -17901,7 +17901,7 @@
       <c r="I602" s="7"/>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A603" s="17" t="s">
+      <c r="A603" s="15" t="s">
         <v>1082</v>
       </c>
       <c r="B603" s="8" t="s">
@@ -17935,7 +17935,7 @@
       <c r="I604" s="7"/>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A605" s="17" t="s">
+      <c r="A605" s="15" t="s">
         <v>1085</v>
       </c>
       <c r="B605" s="8" t="s">
@@ -17969,7 +17969,7 @@
       <c r="I606" s="7"/>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A607" s="17" t="s">
+      <c r="A607" s="15" t="s">
         <v>1088</v>
       </c>
       <c r="B607" s="8" t="s">
@@ -17999,7 +17999,7 @@
       <c r="I608" s="7"/>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A609" s="17" t="s">
+      <c r="A609" s="15" t="s">
         <v>1090</v>
       </c>
       <c r="B609" s="8" t="s">
@@ -18033,7 +18033,7 @@
       <c r="I610" s="7"/>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A611" s="17" t="s">
+      <c r="A611" s="15" t="s">
         <v>1093</v>
       </c>
       <c r="B611" s="8" t="s">
@@ -18063,7 +18063,7 @@
       <c r="I612" s="7"/>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A613" s="17" t="s">
+      <c r="A613" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="B613" s="8" t="s">
@@ -18093,7 +18093,7 @@
       <c r="I614" s="7"/>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A615" s="17" t="s">
+      <c r="A615" s="15" t="s">
         <v>1098</v>
       </c>
       <c r="B615" s="8"/>
@@ -18125,7 +18125,7 @@
       <c r="I616" s="7"/>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A617" s="17" t="s">
+      <c r="A617" s="15" t="s">
         <v>1100</v>
       </c>
       <c r="B617" s="8" t="s">
@@ -18155,7 +18155,7 @@
       <c r="I618" s="7"/>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A619" s="17" t="s">
+      <c r="A619" s="15" t="s">
         <v>1103</v>
       </c>
       <c r="B619" s="8"/>
@@ -18187,7 +18187,7 @@
       <c r="I620" s="7"/>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A621" s="17" t="s">
+      <c r="A621" s="15" t="s">
         <v>1106</v>
       </c>
       <c r="B621" s="8" t="s">
@@ -18217,7 +18217,7 @@
       <c r="I622" s="7"/>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A623" s="17" t="s">
+      <c r="A623" s="15" t="s">
         <v>1109</v>
       </c>
       <c r="B623" s="8"/>
@@ -18245,7 +18245,7 @@
       <c r="I624" s="7"/>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A625" s="17" t="s">
+      <c r="A625" s="15" t="s">
         <v>1111</v>
       </c>
       <c r="B625" s="8"/>
@@ -18273,7 +18273,7 @@
       <c r="I626" s="7"/>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A627" s="17" t="s">
+      <c r="A627" s="15" t="s">
         <v>1113</v>
       </c>
       <c r="B627" s="8"/>
@@ -18305,7 +18305,7 @@
       <c r="I628" s="7"/>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A629" s="17" t="s">
+      <c r="A629" s="15" t="s">
         <v>1115</v>
       </c>
       <c r="B629" s="8"/>
@@ -18337,7 +18337,7 @@
       <c r="I630" s="7"/>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A631" s="17" t="s">
+      <c r="A631" s="15" t="s">
         <v>1117</v>
       </c>
       <c r="B631" s="8"/>
@@ -18422,7 +18422,7 @@
       </c>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A638" s="15" t="s">
+      <c r="A638" s="17" t="s">
         <v>1119</v>
       </c>
       <c r="B638" s="2" t="s">
@@ -18456,7 +18456,7 @@
       <c r="I639" s="7"/>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A640" s="17" t="s">
+      <c r="A640" s="15" t="s">
         <v>1123</v>
       </c>
       <c r="B640" s="8" t="s">
@@ -18486,7 +18486,7 @@
       <c r="I641" s="7"/>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A642" s="17" t="s">
+      <c r="A642" s="15" t="s">
         <v>1126</v>
       </c>
       <c r="B642" s="8" t="s">
@@ -18520,7 +18520,7 @@
       <c r="I643" s="7"/>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A644" s="17" t="s">
+      <c r="A644" s="15" t="s">
         <v>1129</v>
       </c>
       <c r="B644" s="8" t="s">
@@ -18554,7 +18554,7 @@
       <c r="I645" s="7"/>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A646" s="17" t="s">
+      <c r="A646" s="15" t="s">
         <v>993</v>
       </c>
       <c r="B646" s="8" t="s">
@@ -18588,7 +18588,7 @@
       <c r="I647" s="7"/>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A648" s="17" t="s">
+      <c r="A648" s="15" t="s">
         <v>996</v>
       </c>
       <c r="B648" s="8"/>
@@ -18620,7 +18620,7 @@
       <c r="I649" s="7"/>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A650" s="17" t="s">
+      <c r="A650" s="15" t="s">
         <v>1134</v>
       </c>
       <c r="B650" s="8"/>
@@ -18652,7 +18652,7 @@
       <c r="I651" s="7"/>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A652" s="17" t="s">
+      <c r="A652" s="15" t="s">
         <v>1004</v>
       </c>
       <c r="B652" s="8"/>
@@ -18684,7 +18684,7 @@
       <c r="I653" s="7"/>
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A654" s="17" t="s">
+      <c r="A654" s="15" t="s">
         <v>1026</v>
       </c>
       <c r="B654" s="8" t="s">
@@ -18718,7 +18718,7 @@
       <c r="I655" s="7"/>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A656" s="17" t="s">
+      <c r="A656" s="15" t="s">
         <v>1136</v>
       </c>
       <c r="B656" s="8" t="s">
@@ -18752,7 +18752,7 @@
       <c r="I657" s="7"/>
     </row>
     <row r="658" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A658" s="17" t="s">
+      <c r="A658" s="15" t="s">
         <v>1139</v>
       </c>
       <c r="B658" s="8" t="s">
@@ -18786,7 +18786,7 @@
       <c r="I659" s="7"/>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A660" s="17" t="s">
+      <c r="A660" s="15" t="s">
         <v>1142</v>
       </c>
       <c r="B660" s="8"/>
@@ -18818,7 +18818,7 @@
       <c r="I661" s="7"/>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A662" s="17" t="s">
+      <c r="A662" s="15" t="s">
         <v>1144</v>
       </c>
       <c r="B662" s="8"/>
@@ -18850,7 +18850,7 @@
       <c r="I663" s="7"/>
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A664" s="17" t="s">
+      <c r="A664" s="15" t="s">
         <v>1036</v>
       </c>
       <c r="B664" s="8" t="s">
@@ -18884,7 +18884,7 @@
       <c r="I665" s="7"/>
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A666" s="17" t="s">
+      <c r="A666" s="15" t="s">
         <v>1043</v>
       </c>
       <c r="B666" s="8" t="s">
@@ -18918,7 +18918,7 @@
       <c r="I667" s="7"/>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A668" s="17" t="s">
+      <c r="A668" s="15" t="s">
         <v>1148</v>
       </c>
       <c r="B668" s="8" t="s">
@@ -18952,7 +18952,7 @@
       <c r="I669" s="7"/>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A670" s="17" t="s">
+      <c r="A670" s="15" t="s">
         <v>1151</v>
       </c>
       <c r="B670" s="8" t="s">
@@ -18990,7 +18990,7 @@
       <c r="I671" s="7"/>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A672" s="17" t="s">
+      <c r="A672" s="15" t="s">
         <v>1155</v>
       </c>
       <c r="B672" s="8"/>
@@ -19022,7 +19022,7 @@
       <c r="I673" s="7"/>
     </row>
     <row r="674" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A674" s="17" t="s">
+      <c r="A674" s="15" t="s">
         <v>1157</v>
       </c>
       <c r="B674" s="8" t="s">
@@ -19056,7 +19056,7 @@
       <c r="I675" s="7"/>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A676" s="17" t="s">
+      <c r="A676" s="15" t="s">
         <v>1057</v>
       </c>
       <c r="B676" s="8" t="s">
@@ -19090,7 +19090,7 @@
       <c r="I677" s="7"/>
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A678" s="17" t="s">
+      <c r="A678" s="15" t="s">
         <v>1163</v>
       </c>
       <c r="B678" s="8" t="s">
@@ -19124,7 +19124,7 @@
       <c r="I679" s="7"/>
     </row>
     <row r="680" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A680" s="17" t="s">
+      <c r="A680" s="15" t="s">
         <v>1167</v>
       </c>
       <c r="B680" s="8" t="s">
@@ -19158,7 +19158,7 @@
       <c r="I681" s="7"/>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A682" s="17" t="s">
+      <c r="A682" s="15" t="s">
         <v>1170</v>
       </c>
       <c r="B682" s="8"/>
@@ -19190,7 +19190,7 @@
       <c r="I683" s="7"/>
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A684" s="17" t="s">
+      <c r="A684" s="15" t="s">
         <v>1172</v>
       </c>
       <c r="B684" s="8" t="s">
@@ -19224,7 +19224,7 @@
       <c r="I685" s="7"/>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A686" s="17" t="s">
+      <c r="A686" s="15" t="s">
         <v>1175</v>
       </c>
       <c r="B686" s="8" t="s">
@@ -19258,7 +19258,7 @@
       <c r="I687" s="7"/>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A688" s="17" t="s">
+      <c r="A688" s="15" t="s">
         <v>1178</v>
       </c>
       <c r="B688" s="8" t="s">
@@ -19292,7 +19292,7 @@
       <c r="I689" s="7"/>
     </row>
     <row r="690" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A690" s="17" t="s">
+      <c r="A690" s="15" t="s">
         <v>1181</v>
       </c>
       <c r="B690" s="8" t="s">
@@ -19326,7 +19326,7 @@
       <c r="I691" s="7"/>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A692" s="17" t="s">
+      <c r="A692" s="15" t="s">
         <v>1184</v>
       </c>
       <c r="B692" s="8" t="s">
@@ -19360,7 +19360,7 @@
       <c r="I693" s="7"/>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A694" s="17" t="s">
+      <c r="A694" s="15" t="s">
         <v>1187</v>
       </c>
       <c r="B694" s="8" t="s">
@@ -19394,7 +19394,7 @@
       <c r="I695" s="7"/>
     </row>
     <row r="696" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A696" s="17" t="s">
+      <c r="A696" s="15" t="s">
         <v>1190</v>
       </c>
       <c r="B696" s="8" t="s">
@@ -19428,7 +19428,7 @@
       <c r="I697" s="7"/>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A698" s="17" t="s">
+      <c r="A698" s="15" t="s">
         <v>1193</v>
       </c>
       <c r="B698" s="8" t="s">
@@ -19462,7 +19462,7 @@
       <c r="I699" s="7"/>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A700" s="17" t="s">
+      <c r="A700" s="15" t="s">
         <v>1196</v>
       </c>
       <c r="B700" s="8" t="s">
@@ -19496,7 +19496,7 @@
       <c r="I701" s="7"/>
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A702" s="17" t="s">
+      <c r="A702" s="15" t="s">
         <v>1199</v>
       </c>
       <c r="B702" s="8" t="s">
@@ -19530,7 +19530,7 @@
       <c r="I703" s="7"/>
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A704" s="17" t="s">
+      <c r="A704" s="15" t="s">
         <v>1202</v>
       </c>
       <c r="B704" s="8"/>
@@ -19558,7 +19558,7 @@
       <c r="I705" s="7"/>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A706" s="17" t="s">
+      <c r="A706" s="15" t="s">
         <v>1204</v>
       </c>
       <c r="B706" s="8"/>
@@ -19590,7 +19590,7 @@
       <c r="I707" s="7"/>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A708" s="17" t="s">
+      <c r="A708" s="15" t="s">
         <v>1206</v>
       </c>
       <c r="B708" s="8"/>
@@ -19622,7 +19622,7 @@
       <c r="I709" s="7"/>
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A710" s="17" t="s">
+      <c r="A710" s="15" t="s">
         <v>1208</v>
       </c>
       <c r="B710" s="8"/>
@@ -19650,7 +19650,7 @@
       <c r="I711" s="7"/>
     </row>
     <row r="712" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A712" s="17" t="s">
+      <c r="A712" s="15" t="s">
         <v>1210</v>
       </c>
       <c r="B712" s="8"/>
@@ -19682,7 +19682,7 @@
       <c r="I713" s="7"/>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A714" s="17" t="s">
+      <c r="A714" s="15" t="s">
         <v>1212</v>
       </c>
       <c r="B714" s="8"/>
@@ -19714,7 +19714,7 @@
       <c r="I715" s="7"/>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A716" s="17" t="s">
+      <c r="A716" s="15" t="s">
         <v>1214</v>
       </c>
       <c r="B716" s="8"/>
@@ -19742,7 +19742,7 @@
       <c r="I717" s="7"/>
     </row>
     <row r="718" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A718" s="17" t="s">
+      <c r="A718" s="15" t="s">
         <v>1106</v>
       </c>
       <c r="B718" s="8"/>
@@ -19774,7 +19774,7 @@
       <c r="I719" s="7"/>
     </row>
     <row r="720" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A720" s="17" t="s">
+      <c r="A720" s="15" t="s">
         <v>1109</v>
       </c>
       <c r="B720" s="8"/>
@@ -19806,7 +19806,7 @@
       <c r="I721" s="7"/>
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A722" s="17" t="s">
+      <c r="A722" s="15" t="s">
         <v>1218</v>
       </c>
       <c r="B722" s="8"/>
@@ -19838,7 +19838,7 @@
       <c r="I723" s="7"/>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A724" s="17" t="s">
+      <c r="A724" s="15" t="s">
         <v>1220</v>
       </c>
       <c r="B724" s="8"/>
@@ -19923,7 +19923,7 @@
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A731" s="15" t="s">
+      <c r="A731" s="17" t="s">
         <v>973</v>
       </c>
       <c r="B731" s="2" t="s">
@@ -19957,7 +19957,7 @@
       <c r="I732" s="7"/>
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A733" s="17" t="s">
+      <c r="A733" s="15" t="s">
         <v>993</v>
       </c>
       <c r="B733" s="8" t="s">
@@ -19987,7 +19987,7 @@
       <c r="I734" s="7"/>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A735" s="17" t="s">
+      <c r="A735" s="15" t="s">
         <v>1227</v>
       </c>
       <c r="B735" s="8" t="s">
@@ -20021,7 +20021,7 @@
       <c r="I736" s="7"/>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A737" s="17" t="s">
+      <c r="A737" s="15" t="s">
         <v>1231</v>
       </c>
       <c r="B737" s="8"/>
@@ -20057,7 +20057,7 @@
       <c r="I738" s="7"/>
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A739" s="17" t="s">
+      <c r="A739" s="15" t="s">
         <v>1098</v>
       </c>
       <c r="B739" s="8" t="s">
@@ -20089,7 +20089,7 @@
       <c r="I740" s="7"/>
     </row>
     <row r="741" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A741" s="17" t="s">
+      <c r="A741" s="15" t="s">
         <v>1016</v>
       </c>
       <c r="B741" s="8" t="s">
@@ -20123,7 +20123,7 @@
       <c r="I742" s="7"/>
     </row>
     <row r="743" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A743" s="17" t="s">
+      <c r="A743" s="15" t="s">
         <v>967</v>
       </c>
       <c r="B743" s="8"/>
@@ -20155,7 +20155,7 @@
       <c r="I744" s="7"/>
     </row>
     <row r="745" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A745" s="17" t="s">
+      <c r="A745" s="15" t="s">
         <v>1239</v>
       </c>
       <c r="B745" s="8" t="s">
@@ -20189,7 +20189,7 @@
       <c r="I746" s="7"/>
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A747" s="17" t="s">
+      <c r="A747" s="15" t="s">
         <v>1242</v>
       </c>
       <c r="B747" s="8" t="s">
@@ -20223,7 +20223,7 @@
       <c r="I748" s="7"/>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A749" s="17" t="s">
+      <c r="A749" s="15" t="s">
         <v>1039</v>
       </c>
       <c r="B749" s="8"/>
@@ -20251,7 +20251,7 @@
       <c r="I750" s="7"/>
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A751" s="17" t="s">
+      <c r="A751" s="15" t="s">
         <v>1082</v>
       </c>
       <c r="B751" s="8" t="s">
@@ -20285,7 +20285,7 @@
       <c r="I752" s="7"/>
     </row>
     <row r="753" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A753" s="17" t="s">
+      <c r="A753" s="15" t="s">
         <v>1041</v>
       </c>
       <c r="B753" s="8"/>
@@ -20317,7 +20317,7 @@
       <c r="I754" s="7"/>
     </row>
     <row r="755" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A755" s="17" t="s">
+      <c r="A755" s="15" t="s">
         <v>1247</v>
       </c>
       <c r="B755" s="8"/>
@@ -20349,7 +20349,7 @@
       <c r="I756" s="7"/>
     </row>
     <row r="757" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A757" s="17" t="s">
+      <c r="A757" s="15" t="s">
         <v>1043</v>
       </c>
       <c r="B757" s="8" t="s">
@@ -20383,7 +20383,7 @@
       <c r="I758" s="7"/>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A759" s="17" t="s">
+      <c r="A759" s="15" t="s">
         <v>1151</v>
       </c>
       <c r="B759" s="8"/>
@@ -20411,7 +20411,7 @@
       <c r="I760" s="7"/>
     </row>
     <row r="761" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A761" s="17" t="s">
+      <c r="A761" s="15" t="s">
         <v>1250</v>
       </c>
       <c r="B761" s="8" t="s">
@@ -20445,7 +20445,7 @@
       <c r="I762" s="7"/>
     </row>
     <row r="763" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A763" s="17" t="s">
+      <c r="A763" s="15" t="s">
         <v>1093</v>
       </c>
       <c r="B763" s="8" t="s">
@@ -20479,7 +20479,7 @@
       <c r="I764" s="7"/>
     </row>
     <row r="765" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A765" s="17" t="s">
+      <c r="A765" s="15" t="s">
         <v>1255</v>
       </c>
       <c r="B765" s="8" t="s">
@@ -20513,7 +20513,7 @@
       <c r="I766" s="7"/>
     </row>
     <row r="767" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A767" s="17" t="s">
+      <c r="A767" s="15" t="s">
         <v>1258</v>
       </c>
       <c r="B767" s="8" t="s">
@@ -20547,7 +20547,7 @@
       <c r="I768" s="7"/>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A769" s="17" t="s">
+      <c r="A769" s="15" t="s">
         <v>1117</v>
       </c>
       <c r="B769" s="8"/>
@@ -20632,7 +20632,7 @@
       </c>
     </row>
     <row r="776" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A776" s="15" t="s">
+      <c r="A776" s="17" t="s">
         <v>1262</v>
       </c>
       <c r="B776" s="2" t="s">
@@ -20666,7 +20666,7 @@
       <c r="I777" s="7"/>
     </row>
     <row r="778" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A778" s="17" t="s">
+      <c r="A778" s="15" t="s">
         <v>1266</v>
       </c>
       <c r="B778" s="8" t="s">
@@ -20700,7 +20700,7 @@
       <c r="I779" s="7"/>
     </row>
     <row r="780" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A780" s="17" t="s">
+      <c r="A780" s="15" t="s">
         <v>1136</v>
       </c>
       <c r="B780" s="8" t="s">
@@ -20734,7 +20734,7 @@
       <c r="I781" s="7"/>
     </row>
     <row r="782" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A782" s="17" t="s">
+      <c r="A782" s="15" t="s">
         <v>1270</v>
       </c>
       <c r="B782" s="8" t="s">
@@ -20768,7 +20768,7 @@
       <c r="I783" s="7"/>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A784" s="17" t="s">
+      <c r="A784" s="15" t="s">
         <v>1273</v>
       </c>
       <c r="B784" s="8" t="s">
@@ -20802,7 +20802,7 @@
       <c r="I785" s="7"/>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A786" s="17" t="s">
+      <c r="A786" s="15" t="s">
         <v>1170</v>
       </c>
       <c r="B786" s="8" t="s">
@@ -20836,7 +20836,7 @@
       <c r="I787" s="7"/>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A788" s="17" t="s">
+      <c r="A788" s="15" t="s">
         <v>1279</v>
       </c>
       <c r="B788" s="8" t="s">
@@ -20870,7 +20870,7 @@
       <c r="I789" s="7"/>
     </row>
     <row r="790" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A790" s="17" t="s">
+      <c r="A790" s="15" t="s">
         <v>1283</v>
       </c>
       <c r="B790" s="8"/>
@@ -20902,7 +20902,7 @@
       <c r="I791" s="7"/>
     </row>
     <row r="792" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A792" s="17" t="s">
+      <c r="A792" s="15" t="s">
         <v>1142</v>
       </c>
       <c r="B792" s="8"/>
@@ -20934,7 +20934,7 @@
       <c r="I793" s="7"/>
     </row>
     <row r="794" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A794" s="17" t="s">
+      <c r="A794" s="15" t="s">
         <v>1285</v>
       </c>
       <c r="B794" s="8" t="s">
@@ -20968,7 +20968,7 @@
       <c r="I795" s="7"/>
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A796" s="17" t="s">
+      <c r="A796" s="15" t="s">
         <v>1288</v>
       </c>
       <c r="B796" s="8" t="s">
@@ -21002,7 +21002,7 @@
       <c r="I797" s="7"/>
     </row>
     <row r="798" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A798" s="17" t="s">
+      <c r="A798" s="15" t="s">
         <v>1292</v>
       </c>
       <c r="B798" s="8" t="s">
@@ -21036,7 +21036,7 @@
       <c r="I799" s="7"/>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A800" s="17" t="s">
+      <c r="A800" s="15" t="s">
         <v>1295</v>
       </c>
       <c r="B800" s="8" t="s">
@@ -21070,7 +21070,7 @@
       <c r="I801" s="7"/>
     </row>
     <row r="802" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A802" s="17" t="s">
+      <c r="A802" s="15" t="s">
         <v>1298</v>
       </c>
       <c r="B802" s="8" t="s">
@@ -21100,7 +21100,7 @@
       <c r="I803" s="7"/>
     </row>
     <row r="804" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A804" s="17" t="s">
+      <c r="A804" s="15" t="s">
         <v>1302</v>
       </c>
       <c r="B804" s="8" t="s">
@@ -21130,7 +21130,7 @@
       <c r="I805" s="7"/>
     </row>
     <row r="806" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A806" s="17" t="s">
+      <c r="A806" s="15" t="s">
         <v>1305</v>
       </c>
       <c r="B806" s="8" t="s">
@@ -21164,7 +21164,7 @@
       <c r="I807" s="7"/>
     </row>
     <row r="808" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A808" s="17" t="s">
+      <c r="A808" s="15" t="s">
         <v>1309</v>
       </c>
       <c r="B808" s="8" t="s">
@@ -21198,7 +21198,7 @@
       <c r="I809" s="7"/>
     </row>
     <row r="810" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A810" s="17" t="s">
+      <c r="A810" s="15" t="s">
         <v>1313</v>
       </c>
       <c r="B810" s="8" t="s">
@@ -21232,7 +21232,7 @@
       <c r="I811" s="7"/>
     </row>
     <row r="812" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A812" s="17" t="s">
+      <c r="A812" s="15" t="s">
         <v>1316</v>
       </c>
       <c r="B812" s="8">
@@ -21266,7 +21266,7 @@
       <c r="I813" s="7"/>
     </row>
     <row r="814" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A814" s="17" t="s">
+      <c r="A814" s="15" t="s">
         <v>1319</v>
       </c>
       <c r="B814" s="8" t="s">
@@ -21300,7 +21300,7 @@
       <c r="I815" s="7"/>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A816" s="17" t="s">
+      <c r="A816" s="15" t="s">
         <v>1155</v>
       </c>
       <c r="B816" s="8"/>
@@ -21332,7 +21332,7 @@
       <c r="I817" s="7"/>
     </row>
     <row r="818" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A818" s="17" t="s">
+      <c r="A818" s="15" t="s">
         <v>1323</v>
       </c>
       <c r="B818" s="8" t="s">
@@ -21366,7 +21366,7 @@
       <c r="I819" s="7"/>
     </row>
     <row r="820" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A820" s="17" t="s">
+      <c r="A820" s="15" t="s">
         <v>1148</v>
       </c>
       <c r="B820" s="8" t="s">
@@ -21400,7 +21400,7 @@
       <c r="I821" s="7"/>
     </row>
     <row r="822" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A822" s="17" t="s">
+      <c r="A822" s="15" t="s">
         <v>1328</v>
       </c>
       <c r="B822" s="8" t="s">
@@ -21434,7 +21434,7 @@
       <c r="I823" s="7"/>
     </row>
     <row r="824" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A824" s="17" t="s">
+      <c r="A824" s="15" t="s">
         <v>1331</v>
       </c>
       <c r="B824" s="8" t="s">
@@ -21468,7 +21468,7 @@
       <c r="I825" s="7"/>
     </row>
     <row r="826" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A826" s="17" t="s">
+      <c r="A826" s="15" t="s">
         <v>1334</v>
       </c>
       <c r="B826" s="8" t="s">
@@ -21502,7 +21502,7 @@
       <c r="I827" s="7"/>
     </row>
     <row r="828" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A828" s="17" t="s">
+      <c r="A828" s="15" t="s">
         <v>1338</v>
       </c>
       <c r="B828" s="8" t="s">
@@ -21532,7 +21532,7 @@
       <c r="I829" s="7"/>
     </row>
     <row r="830" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A830" s="17" t="s">
+      <c r="A830" s="15" t="s">
         <v>1341</v>
       </c>
       <c r="B830" s="8" t="s">
@@ -21566,7 +21566,7 @@
       <c r="I831" s="7"/>
     </row>
     <row r="832" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A832" s="17" t="s">
+      <c r="A832" s="15" t="s">
         <v>1012</v>
       </c>
       <c r="B832" s="8" t="s">
@@ -21600,7 +21600,7 @@
       <c r="I833" s="7"/>
     </row>
     <row r="834" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A834" s="17" t="s">
+      <c r="A834" s="15" t="s">
         <v>1344</v>
       </c>
       <c r="B834" s="8" t="s">
@@ -21634,7 +21634,7 @@
       <c r="I835" s="7"/>
     </row>
     <row r="836" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A836" s="17" t="s">
+      <c r="A836" s="15" t="s">
         <v>1193</v>
       </c>
       <c r="B836" s="8" t="s">
@@ -21664,7 +21664,7 @@
       <c r="I837" s="7"/>
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A838" s="17" t="s">
+      <c r="A838" s="15" t="s">
         <v>1349</v>
       </c>
       <c r="B838" s="8" t="s">
@@ -21698,7 +21698,7 @@
       <c r="I839" s="7"/>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A840" s="17" t="s">
+      <c r="A840" s="15" t="s">
         <v>1352</v>
       </c>
       <c r="B840" s="8" t="s">
@@ -21728,7 +21728,7 @@
       <c r="I841" s="7"/>
     </row>
     <row r="842" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A842" s="17" t="s">
+      <c r="A842" s="15" t="s">
         <v>1355</v>
       </c>
       <c r="B842" s="8" t="s">
@@ -21758,7 +21758,7 @@
       <c r="I843" s="7"/>
     </row>
     <row r="844" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A844" s="17" t="s">
+      <c r="A844" s="15" t="s">
         <v>1358</v>
       </c>
       <c r="B844" s="8" t="s">
@@ -21792,7 +21792,7 @@
       <c r="I845" s="7"/>
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A846" s="17" t="s">
+      <c r="A846" s="15" t="s">
         <v>1157</v>
       </c>
       <c r="B846" s="8" t="s">
@@ -21826,7 +21826,7 @@
       <c r="I847" s="7"/>
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A848" s="17" t="s">
+      <c r="A848" s="15" t="s">
         <v>1361</v>
       </c>
       <c r="B848" s="8" t="s">
@@ -21860,7 +21860,7 @@
       <c r="I849" s="7"/>
     </row>
     <row r="850" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A850" s="17" t="s">
+      <c r="A850" s="15" t="s">
         <v>1364</v>
       </c>
       <c r="B850" s="8"/>
@@ -21892,7 +21892,7 @@
       <c r="I851" s="7"/>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A852" s="17" t="s">
+      <c r="A852" s="15" t="s">
         <v>1366</v>
       </c>
       <c r="B852" s="8"/>
@@ -21924,7 +21924,7 @@
       <c r="I853" s="7"/>
     </row>
     <row r="854" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A854" s="17" t="s">
+      <c r="A854" s="15" t="s">
         <v>1368</v>
       </c>
       <c r="B854" s="8"/>
@@ -21956,7 +21956,7 @@
       <c r="I855" s="7"/>
     </row>
     <row r="856" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A856" s="17" t="s">
+      <c r="A856" s="15" t="s">
         <v>1370</v>
       </c>
       <c r="B856" s="8" t="s">
@@ -21990,7 +21990,7 @@
       <c r="I857" s="7"/>
     </row>
     <row r="858" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A858" s="17" t="s">
+      <c r="A858" s="15" t="s">
         <v>1373</v>
       </c>
       <c r="B858" s="8" t="s">
@@ -22024,7 +22024,7 @@
       <c r="I859" s="7"/>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A860" s="17" t="s">
+      <c r="A860" s="15" t="s">
         <v>1377</v>
       </c>
       <c r="B860" s="8" t="s">
@@ -22058,7 +22058,7 @@
       <c r="I861" s="7"/>
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A862" s="17" t="s">
+      <c r="A862" s="15" t="s">
         <v>1381</v>
       </c>
       <c r="B862" s="8"/>
@@ -22090,7 +22090,7 @@
       <c r="I863" s="7"/>
     </row>
     <row r="864" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A864" s="17" t="s">
+      <c r="A864" s="15" t="s">
         <v>1383</v>
       </c>
       <c r="B864" s="8"/>
@@ -22126,7 +22126,7 @@
       <c r="I865" s="7"/>
     </row>
     <row r="866" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A866" s="17" t="s">
+      <c r="A866" s="15" t="s">
         <v>1385</v>
       </c>
       <c r="B866" s="8" t="s">
@@ -22160,7 +22160,7 @@
       <c r="I867" s="7"/>
     </row>
     <row r="868" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A868" s="17" t="s">
+      <c r="A868" s="15" t="s">
         <v>1388</v>
       </c>
       <c r="B868" s="8" t="s">
@@ -22194,7 +22194,7 @@
       <c r="I869" s="7"/>
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A870" s="17" t="s">
+      <c r="A870" s="15" t="s">
         <v>1391</v>
       </c>
       <c r="B870" s="8" t="s">
@@ -22228,7 +22228,7 @@
       <c r="I871" s="7"/>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A872" s="17" t="s">
+      <c r="A872" s="15" t="s">
         <v>1394</v>
       </c>
       <c r="B872" s="8" t="s">
@@ -22262,7 +22262,7 @@
       <c r="I873" s="7"/>
     </row>
     <row r="874" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A874" s="17" t="s">
+      <c r="A874" s="15" t="s">
         <v>1397</v>
       </c>
       <c r="B874" s="8" t="s">
@@ -22296,7 +22296,7 @@
       <c r="I875" s="7"/>
     </row>
     <row r="876" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A876" s="17" t="s">
+      <c r="A876" s="15" t="s">
         <v>1401</v>
       </c>
       <c r="B876" s="8" t="s">
@@ -22330,7 +22330,7 @@
       <c r="I877" s="7"/>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A878" s="17" t="s">
+      <c r="A878" s="15" t="s">
         <v>1404</v>
       </c>
       <c r="B878" s="8"/>
@@ -22362,7 +22362,7 @@
       <c r="I879" s="7"/>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A880" s="17" t="s">
+      <c r="A880" s="15" t="s">
         <v>1123</v>
       </c>
       <c r="B880" s="8" t="s">
@@ -22396,7 +22396,7 @@
       <c r="I881" s="7"/>
     </row>
     <row r="882" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A882" s="17" t="s">
+      <c r="A882" s="15" t="s">
         <v>1175</v>
       </c>
       <c r="B882" s="8" t="s">
@@ -22498,7 +22498,7 @@
       </c>
     </row>
     <row r="889" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A889" s="15" t="s">
+      <c r="A889" s="17" t="s">
         <v>1409</v>
       </c>
       <c r="B889" s="2" t="s">
@@ -22538,7 +22538,7 @@
       <c r="L890" s="7"/>
     </row>
     <row r="891" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A891" s="17" t="s">
+      <c r="A891" s="15" t="s">
         <v>1412</v>
       </c>
       <c r="B891" s="8" t="s">
@@ -22578,7 +22578,7 @@
       <c r="L892" s="7"/>
     </row>
     <row r="893" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A893" s="17" t="s">
+      <c r="A893" s="15" t="s">
         <v>1415</v>
       </c>
       <c r="B893" s="8" t="s">
@@ -22622,7 +22622,7 @@
       <c r="L894" s="7"/>
     </row>
     <row r="895" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A895" s="17" t="s">
+      <c r="A895" s="15" t="s">
         <v>1418</v>
       </c>
       <c r="B895" s="8" t="s">
@@ -22662,7 +22662,7 @@
       <c r="L896" s="7"/>
     </row>
     <row r="897" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A897" s="17" t="s">
+      <c r="A897" s="15" t="s">
         <v>1421</v>
       </c>
       <c r="B897" s="8"/>
@@ -22704,7 +22704,7 @@
       <c r="L898" s="7"/>
     </row>
     <row r="899" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A899" s="17" t="s">
+      <c r="A899" s="15" t="s">
         <v>1423</v>
       </c>
       <c r="B899" s="8" t="s">
@@ -22744,7 +22744,7 @@
       <c r="L900" s="7"/>
     </row>
     <row r="901" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A901" s="17" t="s">
+      <c r="A901" s="15" t="s">
         <v>1426</v>
       </c>
       <c r="B901" s="8" t="s">
@@ -22788,7 +22788,7 @@
       <c r="L902" s="7"/>
     </row>
     <row r="903" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A903" s="17" t="s">
+      <c r="A903" s="15" t="s">
         <v>1429</v>
       </c>
       <c r="B903" s="8" t="s">
@@ -22828,7 +22828,7 @@
       <c r="L904" s="7"/>
     </row>
     <row r="905" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A905" s="17" t="s">
+      <c r="A905" s="15" t="s">
         <v>1432</v>
       </c>
       <c r="B905" s="8" t="s">
@@ -22864,7 +22864,7 @@
       <c r="L906" s="7"/>
     </row>
     <row r="907" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A907" s="17" t="s">
+      <c r="A907" s="15" t="s">
         <v>1434</v>
       </c>
       <c r="B907" s="8" t="s">
@@ -22904,7 +22904,7 @@
       <c r="L908" s="7"/>
     </row>
     <row r="909" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A909" s="17" t="s">
+      <c r="A909" s="15" t="s">
         <v>1437</v>
       </c>
       <c r="B909" s="8" t="s">
@@ -22940,7 +22940,7 @@
       <c r="L910" s="7"/>
     </row>
     <row r="911" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A911" s="17" t="s">
+      <c r="A911" s="15" t="s">
         <v>1439</v>
       </c>
       <c r="B911" s="8" t="s">
@@ -22984,7 +22984,7 @@
       <c r="L912" s="7"/>
     </row>
     <row r="913" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A913" s="17" t="s">
+      <c r="A913" s="15" t="s">
         <v>1442</v>
       </c>
       <c r="B913" s="8" t="s">
@@ -23028,7 +23028,7 @@
       <c r="L914" s="7"/>
     </row>
     <row r="915" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A915" s="17" t="s">
+      <c r="A915" s="15" t="s">
         <v>1445</v>
       </c>
       <c r="B915" s="8"/>
@@ -23066,7 +23066,7 @@
       <c r="L916" s="7"/>
     </row>
     <row r="917" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A917" s="17" t="s">
+      <c r="A917" s="15" t="s">
         <v>1447</v>
       </c>
       <c r="B917" s="8" t="s">
@@ -23106,7 +23106,7 @@
       <c r="L918" s="7"/>
     </row>
     <row r="919" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A919" s="17" t="s">
+      <c r="A919" s="15" t="s">
         <v>1450</v>
       </c>
       <c r="B919" s="8" t="s">
@@ -23146,7 +23146,7 @@
       <c r="L920" s="7"/>
     </row>
     <row r="921" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A921" s="17" t="s">
+      <c r="A921" s="15" t="s">
         <v>1453</v>
       </c>
       <c r="B921" s="8" t="s">
@@ -23194,7 +23194,7 @@
       <c r="L922" s="7"/>
     </row>
     <row r="923" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A923" s="17" t="s">
+      <c r="A923" s="15" t="s">
         <v>1456</v>
       </c>
       <c r="B923" s="8"/>
@@ -23232,7 +23232,7 @@
       <c r="L924" s="7"/>
     </row>
     <row r="925" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A925" s="17" t="s">
+      <c r="A925" s="15" t="s">
         <v>1458</v>
       </c>
       <c r="B925" s="8"/>
@@ -23274,7 +23274,7 @@
       <c r="L926" s="7"/>
     </row>
     <row r="927" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A927" s="17" t="s">
+      <c r="A927" s="15" t="s">
         <v>1460</v>
       </c>
       <c r="B927" s="8" t="s">
@@ -23314,7 +23314,7 @@
       <c r="L928" s="7"/>
     </row>
     <row r="929" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A929" s="17" t="s">
+      <c r="A929" s="15" t="s">
         <v>939</v>
       </c>
       <c r="B929" s="8"/>
@@ -23356,7 +23356,7 @@
       <c r="L930" s="7"/>
     </row>
     <row r="931" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A931" s="17" t="s">
+      <c r="A931" s="15" t="s">
         <v>1464</v>
       </c>
       <c r="B931" s="8" t="s">
@@ -23400,7 +23400,7 @@
       <c r="L932" s="7"/>
     </row>
     <row r="933" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A933" s="17" t="s">
+      <c r="A933" s="15" t="s">
         <v>1467</v>
       </c>
       <c r="B933" s="8" t="s">
@@ -23444,7 +23444,7 @@
       <c r="L934" s="7"/>
     </row>
     <row r="935" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A935" s="17" t="s">
+      <c r="A935" s="15" t="s">
         <v>1470</v>
       </c>
       <c r="B935" s="8" t="s">
@@ -23484,7 +23484,7 @@
       <c r="L936" s="7"/>
     </row>
     <row r="937" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A937" s="17" t="s">
+      <c r="A937" s="15" t="s">
         <v>1473</v>
       </c>
       <c r="B937" s="8"/>
@@ -23518,7 +23518,7 @@
       <c r="L938" s="7"/>
     </row>
     <row r="939" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A939" s="17" t="s">
+      <c r="A939" s="15" t="s">
         <v>1474</v>
       </c>
       <c r="B939" s="8" t="s">
@@ -23554,7 +23554,7 @@
       <c r="L940" s="7"/>
     </row>
     <row r="941" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A941" s="17" t="s">
+      <c r="A941" s="15" t="s">
         <v>1476</v>
       </c>
       <c r="B941" s="8" t="s">
@@ -23594,7 +23594,7 @@
       <c r="L942" s="7"/>
     </row>
     <row r="943" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A943" s="17" t="s">
+      <c r="A943" s="15" t="s">
         <v>1479</v>
       </c>
       <c r="B943" s="8"/>
@@ -23636,7 +23636,7 @@
       <c r="L944" s="7"/>
     </row>
     <row r="945" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A945" s="17" t="s">
+      <c r="A945" s="15" t="s">
         <v>1481</v>
       </c>
       <c r="B945" s="8"/>
@@ -23670,7 +23670,7 @@
       <c r="L946" s="7"/>
     </row>
     <row r="947" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A947" s="17" t="s">
+      <c r="A947" s="15" t="s">
         <v>1482</v>
       </c>
       <c r="B947" s="8"/>
@@ -23712,7 +23712,7 @@
       <c r="L948" s="7"/>
     </row>
     <row r="949" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A949" s="17" t="s">
+      <c r="A949" s="15" t="s">
         <v>1484</v>
       </c>
       <c r="B949" s="8" t="s">
@@ -23752,7 +23752,7 @@
       <c r="L950" s="7"/>
     </row>
     <row r="951" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A951" s="17" t="s">
+      <c r="A951" s="15" t="s">
         <v>1487</v>
       </c>
       <c r="B951" s="8" t="s">
@@ -23792,7 +23792,7 @@
       <c r="L952" s="7"/>
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A953" s="17" t="s">
+      <c r="A953" s="15" t="s">
         <v>1490</v>
       </c>
       <c r="B953" s="8" t="s">
@@ -23832,7 +23832,7 @@
       <c r="L954" s="7"/>
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A955" s="17" t="s">
+      <c r="A955" s="15" t="s">
         <v>1493</v>
       </c>
       <c r="B955" s="8" t="s">
@@ -23872,7 +23872,7 @@
       <c r="L956" s="7"/>
     </row>
     <row r="957" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A957" s="17" t="s">
+      <c r="A957" s="15" t="s">
         <v>1496</v>
       </c>
       <c r="B957" s="8" t="s">
@@ -23916,7 +23916,7 @@
       <c r="L958" s="7"/>
     </row>
     <row r="959" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A959" s="17" t="s">
+      <c r="A959" s="15" t="s">
         <v>1499</v>
       </c>
       <c r="B959" s="8"/>
@@ -23962,7 +23962,7 @@
       <c r="L960" s="7"/>
     </row>
     <row r="961" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A961" s="17" t="s">
+      <c r="A961" s="15" t="s">
         <v>1501</v>
       </c>
       <c r="B961" s="8" t="s">
@@ -23998,7 +23998,7 @@
       <c r="L962" s="7"/>
     </row>
     <row r="963" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A963" s="17" t="s">
+      <c r="A963" s="15" t="s">
         <v>1503</v>
       </c>
       <c r="B963" s="8"/>
@@ -24040,7 +24040,7 @@
       <c r="L964" s="7"/>
     </row>
     <row r="965" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A965" s="17" t="s">
+      <c r="A965" s="15" t="s">
         <v>1505</v>
       </c>
       <c r="B965" s="8" t="s">
@@ -24088,7 +24088,7 @@
       <c r="L966" s="7"/>
     </row>
     <row r="967" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A967" s="17" t="s">
+      <c r="A967" s="15" t="s">
         <v>1507</v>
       </c>
       <c r="B967" s="8"/>
@@ -24122,7 +24122,7 @@
       <c r="L968" s="7"/>
     </row>
     <row r="969" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A969" s="17" t="s">
+      <c r="A969" s="15" t="s">
         <v>1508</v>
       </c>
       <c r="B969" s="8"/>
@@ -24160,7 +24160,7 @@
       <c r="L970" s="7"/>
     </row>
     <row r="971" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A971" s="17" t="s">
+      <c r="A971" s="15" t="s">
         <v>1510</v>
       </c>
       <c r="B971" s="8"/>
@@ -24194,7 +24194,7 @@
       <c r="L972" s="7"/>
     </row>
     <row r="973" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A973" s="17" t="s">
+      <c r="A973" s="15" t="s">
         <v>1511</v>
       </c>
       <c r="B973" s="8"/>
@@ -24228,7 +24228,7 @@
       <c r="L974" s="7"/>
     </row>
     <row r="975" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A975" s="17" t="s">
+      <c r="A975" s="15" t="s">
         <v>1512</v>
       </c>
       <c r="B975" s="8"/>
@@ -24266,7 +24266,7 @@
       <c r="L976" s="7"/>
     </row>
     <row r="977" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A977" s="17" t="s">
+      <c r="A977" s="15" t="s">
         <v>1514</v>
       </c>
       <c r="B977" s="8"/>
@@ -24304,7 +24304,7 @@
       <c r="L978" s="7"/>
     </row>
     <row r="979" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A979" s="17" t="s">
+      <c r="A979" s="15" t="s">
         <v>1516</v>
       </c>
       <c r="B979" s="8"/>
@@ -24346,7 +24346,7 @@
       <c r="L980" s="7"/>
     </row>
     <row r="981" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A981" s="17" t="s">
+      <c r="A981" s="15" t="s">
         <v>1518</v>
       </c>
       <c r="B981" s="8"/>
@@ -24384,7 +24384,7 @@
       <c r="L982" s="7"/>
     </row>
     <row r="983" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A983" s="17" t="s">
+      <c r="A983" s="15" t="s">
         <v>1520</v>
       </c>
       <c r="B983" s="8"/>
@@ -24422,7 +24422,7 @@
       <c r="L984" s="7"/>
     </row>
     <row r="985" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A985" s="17" t="s">
+      <c r="A985" s="15" t="s">
         <v>1522</v>
       </c>
       <c r="B985" s="8"/>
@@ -24460,7 +24460,7 @@
       <c r="L986" s="7"/>
     </row>
     <row r="987" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A987" s="17" t="s">
+      <c r="A987" s="15" t="s">
         <v>1524</v>
       </c>
       <c r="B987" s="8" t="s">
@@ -24500,7 +24500,7 @@
       <c r="L988" s="7"/>
     </row>
     <row r="989" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A989" s="17" t="s">
+      <c r="A989" s="15" t="s">
         <v>1527</v>
       </c>
       <c r="B989" s="8" t="s">
@@ -24540,7 +24540,7 @@
       <c r="L990" s="7"/>
     </row>
     <row r="991" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A991" s="17" t="s">
+      <c r="A991" s="15" t="s">
         <v>956</v>
       </c>
       <c r="B991" s="8" t="s">
@@ -24592,7 +24592,7 @@
       <c r="L992" s="7"/>
     </row>
     <row r="993" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A993" s="17" t="s">
+      <c r="A993" s="15" t="s">
         <v>952</v>
       </c>
       <c r="B993" s="8" t="s">
@@ -24636,7 +24636,7 @@
       <c r="L994" s="7"/>
     </row>
     <row r="995" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A995" s="17" t="s">
+      <c r="A995" s="15" t="s">
         <v>1531</v>
       </c>
       <c r="B995" s="8"/>
@@ -24678,7 +24678,7 @@
       <c r="L996" s="7"/>
     </row>
     <row r="997" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A997" s="17" t="s">
+      <c r="A997" s="15" t="s">
         <v>1533</v>
       </c>
       <c r="B997" s="8"/>
@@ -24773,7 +24773,7 @@
       </c>
     </row>
     <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1004" s="15" t="s">
+      <c r="A1004" s="17" t="s">
         <v>1568</v>
       </c>
       <c r="B1004" s="2" t="s">
@@ -24803,7 +24803,7 @@
       <c r="I1005" s="7"/>
     </row>
     <row r="1006" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1006" s="17" t="s">
+      <c r="A1006" s="15" t="s">
         <v>820</v>
       </c>
       <c r="B1006" s="8"/>
@@ -24884,7 +24884,7 @@
       </c>
     </row>
     <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1013" s="15" t="s">
+      <c r="A1013" s="17" t="s">
         <v>1573</v>
       </c>
       <c r="B1013" s="2"/>
@@ -24910,7 +24910,7 @@
       <c r="I1014" s="7"/>
     </row>
     <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1015" s="17" t="s">
+      <c r="A1015" s="15" t="s">
         <v>1574</v>
       </c>
       <c r="B1015" s="8"/>
@@ -24938,7 +24938,7 @@
       <c r="I1016" s="7"/>
     </row>
     <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1017" s="17" t="s">
+      <c r="A1017" s="15" t="s">
         <v>1576</v>
       </c>
       <c r="B1017" s="8"/>
@@ -24970,7 +24970,7 @@
       <c r="I1018" s="7"/>
     </row>
     <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1019" s="17" t="s">
+      <c r="A1019" s="15" t="s">
         <v>1578</v>
       </c>
       <c r="B1019" s="8"/>
@@ -24998,7 +24998,7 @@
       <c r="I1020" s="7"/>
     </row>
     <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1021" s="17" t="s">
+      <c r="A1021" s="15" t="s">
         <v>1580</v>
       </c>
       <c r="B1021" s="8"/>
@@ -25026,7 +25026,7 @@
       <c r="I1022" s="7"/>
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1023" s="17" t="s">
+      <c r="A1023" s="15" t="s">
         <v>1720</v>
       </c>
       <c r="B1023" s="8"/>
@@ -25058,7 +25058,7 @@
       <c r="I1024" s="7"/>
     </row>
     <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1025" s="17" t="s">
+      <c r="A1025" s="15" t="s">
         <v>1722</v>
       </c>
       <c r="B1025" s="8"/>
@@ -25091,6 +25091,490 @@
     </row>
   </sheetData>
   <mergeCells count="508">
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="A1019:A1020"/>
+    <mergeCell ref="A1021:A1022"/>
+    <mergeCell ref="A1006:A1007"/>
+    <mergeCell ref="A1013:A1014"/>
+    <mergeCell ref="A1015:A1016"/>
+    <mergeCell ref="A1010:I1010"/>
+    <mergeCell ref="A1011:I1011"/>
+    <mergeCell ref="A995:A996"/>
+    <mergeCell ref="A997:A998"/>
+    <mergeCell ref="A1001:I1001"/>
+    <mergeCell ref="A1002:I1002"/>
+    <mergeCell ref="A1004:A1005"/>
+    <mergeCell ref="A985:A986"/>
+    <mergeCell ref="A987:A988"/>
+    <mergeCell ref="A989:A990"/>
+    <mergeCell ref="A991:A992"/>
+    <mergeCell ref="A993:A994"/>
+    <mergeCell ref="A975:A976"/>
+    <mergeCell ref="A977:A978"/>
+    <mergeCell ref="A979:A980"/>
+    <mergeCell ref="A981:A982"/>
+    <mergeCell ref="A983:A984"/>
+    <mergeCell ref="A967:A968"/>
+    <mergeCell ref="A969:A970"/>
+    <mergeCell ref="A971:A972"/>
+    <mergeCell ref="A973:A974"/>
+    <mergeCell ref="A957:A958"/>
+    <mergeCell ref="A959:A960"/>
+    <mergeCell ref="A961:A962"/>
+    <mergeCell ref="A963:A964"/>
+    <mergeCell ref="A965:A966"/>
+    <mergeCell ref="A947:A948"/>
+    <mergeCell ref="A949:A950"/>
+    <mergeCell ref="A951:A952"/>
+    <mergeCell ref="A953:A954"/>
+    <mergeCell ref="A955:A956"/>
+    <mergeCell ref="A937:A938"/>
+    <mergeCell ref="A939:A940"/>
+    <mergeCell ref="A941:A942"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="A945:A946"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="A929:A930"/>
+    <mergeCell ref="A931:A932"/>
+    <mergeCell ref="A933:A934"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="A917:A918"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="A921:A922"/>
+    <mergeCell ref="A923:A924"/>
+    <mergeCell ref="A925:A926"/>
+    <mergeCell ref="A907:A908"/>
+    <mergeCell ref="A909:A910"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="A913:A914"/>
+    <mergeCell ref="A915:A916"/>
+    <mergeCell ref="A897:A898"/>
+    <mergeCell ref="A899:A900"/>
+    <mergeCell ref="A901:A902"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="A905:A906"/>
+    <mergeCell ref="A891:A892"/>
+    <mergeCell ref="A886:L886"/>
+    <mergeCell ref="A887:L887"/>
+    <mergeCell ref="A893:A894"/>
+    <mergeCell ref="A895:A896"/>
+    <mergeCell ref="A880:A881"/>
+    <mergeCell ref="A882:A883"/>
+    <mergeCell ref="A889:A890"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="A872:A873"/>
+    <mergeCell ref="A874:A875"/>
+    <mergeCell ref="A876:A877"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="A860:A861"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="A864:A865"/>
+    <mergeCell ref="A866:A867"/>
+    <mergeCell ref="A868:A869"/>
+    <mergeCell ref="A850:A851"/>
+    <mergeCell ref="A852:A853"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="A856:A857"/>
+    <mergeCell ref="A858:A859"/>
+    <mergeCell ref="A840:A841"/>
+    <mergeCell ref="A842:A843"/>
+    <mergeCell ref="A844:A845"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="A848:A849"/>
+    <mergeCell ref="A830:A831"/>
+    <mergeCell ref="A832:A833"/>
+    <mergeCell ref="A834:A835"/>
+    <mergeCell ref="A836:A837"/>
+    <mergeCell ref="A838:A839"/>
+    <mergeCell ref="A820:A821"/>
+    <mergeCell ref="A822:A823"/>
+    <mergeCell ref="A824:A825"/>
+    <mergeCell ref="A826:A827"/>
+    <mergeCell ref="A828:A829"/>
+    <mergeCell ref="A810:A811"/>
+    <mergeCell ref="A812:A813"/>
+    <mergeCell ref="A814:A815"/>
+    <mergeCell ref="A816:A817"/>
+    <mergeCell ref="A818:A819"/>
+    <mergeCell ref="A800:A801"/>
+    <mergeCell ref="A802:A803"/>
+    <mergeCell ref="A804:A805"/>
+    <mergeCell ref="A806:A807"/>
+    <mergeCell ref="A808:A809"/>
+    <mergeCell ref="A790:A791"/>
+    <mergeCell ref="A792:A793"/>
+    <mergeCell ref="A794:A795"/>
+    <mergeCell ref="A796:A797"/>
+    <mergeCell ref="A798:A799"/>
+    <mergeCell ref="A780:A781"/>
+    <mergeCell ref="A782:A783"/>
+    <mergeCell ref="A784:A785"/>
+    <mergeCell ref="A786:A787"/>
+    <mergeCell ref="A788:A789"/>
+    <mergeCell ref="A776:A777"/>
+    <mergeCell ref="A778:A779"/>
+    <mergeCell ref="A773:I773"/>
+    <mergeCell ref="A774:I774"/>
+    <mergeCell ref="A763:A764"/>
+    <mergeCell ref="A765:A766"/>
+    <mergeCell ref="A767:A768"/>
+    <mergeCell ref="A769:A770"/>
+    <mergeCell ref="A753:A754"/>
+    <mergeCell ref="A755:A756"/>
+    <mergeCell ref="A757:A758"/>
+    <mergeCell ref="A759:A760"/>
+    <mergeCell ref="A761:A762"/>
+    <mergeCell ref="A743:A744"/>
+    <mergeCell ref="A745:A746"/>
+    <mergeCell ref="A747:A748"/>
+    <mergeCell ref="A749:A750"/>
+    <mergeCell ref="A751:A752"/>
+    <mergeCell ref="A733:A734"/>
+    <mergeCell ref="A735:A736"/>
+    <mergeCell ref="A737:A738"/>
+    <mergeCell ref="A739:A740"/>
+    <mergeCell ref="A741:A742"/>
+    <mergeCell ref="A722:A723"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="A728:I728"/>
+    <mergeCell ref="A729:I729"/>
+    <mergeCell ref="A731:A732"/>
+    <mergeCell ref="A712:A713"/>
+    <mergeCell ref="A714:A715"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="A718:A719"/>
+    <mergeCell ref="A720:A721"/>
+    <mergeCell ref="A702:A703"/>
+    <mergeCell ref="A704:A705"/>
+    <mergeCell ref="A706:A707"/>
+    <mergeCell ref="A708:A709"/>
+    <mergeCell ref="A710:A711"/>
+    <mergeCell ref="A692:A693"/>
+    <mergeCell ref="A694:A695"/>
+    <mergeCell ref="A696:A697"/>
+    <mergeCell ref="A698:A699"/>
+    <mergeCell ref="A700:A701"/>
+    <mergeCell ref="A682:A683"/>
+    <mergeCell ref="A684:A685"/>
+    <mergeCell ref="A686:A687"/>
+    <mergeCell ref="A688:A689"/>
+    <mergeCell ref="A690:A691"/>
+    <mergeCell ref="A672:A673"/>
+    <mergeCell ref="A674:A675"/>
+    <mergeCell ref="A676:A677"/>
+    <mergeCell ref="A678:A679"/>
+    <mergeCell ref="A680:A681"/>
+    <mergeCell ref="A662:A663"/>
+    <mergeCell ref="A664:A665"/>
+    <mergeCell ref="A666:A667"/>
+    <mergeCell ref="A668:A669"/>
+    <mergeCell ref="A670:A671"/>
+    <mergeCell ref="A652:A653"/>
+    <mergeCell ref="A654:A655"/>
+    <mergeCell ref="A656:A657"/>
+    <mergeCell ref="A658:A659"/>
+    <mergeCell ref="A660:A661"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="A644:A645"/>
+    <mergeCell ref="A646:A647"/>
+    <mergeCell ref="A648:A649"/>
+    <mergeCell ref="A650:A651"/>
+    <mergeCell ref="A631:A632"/>
+    <mergeCell ref="A635:I635"/>
+    <mergeCell ref="A636:I636"/>
+    <mergeCell ref="A638:A639"/>
+    <mergeCell ref="A640:A641"/>
+    <mergeCell ref="A621:A622"/>
+    <mergeCell ref="A623:A624"/>
+    <mergeCell ref="A625:A626"/>
+    <mergeCell ref="A627:A628"/>
+    <mergeCell ref="A629:A630"/>
+    <mergeCell ref="A611:A612"/>
+    <mergeCell ref="A613:A614"/>
+    <mergeCell ref="A615:A616"/>
+    <mergeCell ref="A617:A618"/>
+    <mergeCell ref="A619:A620"/>
+    <mergeCell ref="A601:A602"/>
+    <mergeCell ref="A603:A604"/>
+    <mergeCell ref="A605:A606"/>
+    <mergeCell ref="A607:A608"/>
+    <mergeCell ref="A609:A610"/>
+    <mergeCell ref="A591:A592"/>
+    <mergeCell ref="A593:A594"/>
+    <mergeCell ref="A595:A596"/>
+    <mergeCell ref="A597:A598"/>
+    <mergeCell ref="A599:A600"/>
+    <mergeCell ref="A581:A582"/>
+    <mergeCell ref="A583:A584"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="A587:A588"/>
+    <mergeCell ref="A589:A590"/>
+    <mergeCell ref="A571:A572"/>
+    <mergeCell ref="A573:A574"/>
+    <mergeCell ref="A575:A576"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="A579:A580"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="A563:A564"/>
+    <mergeCell ref="A565:A566"/>
+    <mergeCell ref="A567:A568"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="A551:A552"/>
+    <mergeCell ref="A553:A554"/>
+    <mergeCell ref="A555:A556"/>
+    <mergeCell ref="A557:A558"/>
+    <mergeCell ref="A559:A560"/>
+    <mergeCell ref="A541:A542"/>
+    <mergeCell ref="A543:A544"/>
+    <mergeCell ref="A545:A546"/>
+    <mergeCell ref="A547:A548"/>
+    <mergeCell ref="A549:A550"/>
+    <mergeCell ref="A531:A532"/>
+    <mergeCell ref="A533:A534"/>
+    <mergeCell ref="A535:A536"/>
+    <mergeCell ref="A537:A538"/>
+    <mergeCell ref="A539:A540"/>
+    <mergeCell ref="A522:A523"/>
+    <mergeCell ref="A526:I526"/>
+    <mergeCell ref="A527:I527"/>
+    <mergeCell ref="A529:A530"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="A514:A515"/>
+    <mergeCell ref="A516:A517"/>
+    <mergeCell ref="A518:A519"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="A484:A485"/>
+    <mergeCell ref="A486:A487"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="A431:A432"/>
+    <mergeCell ref="A433:A434"/>
+    <mergeCell ref="A435:A436"/>
+    <mergeCell ref="A437:A438"/>
+    <mergeCell ref="A441:I441"/>
+    <mergeCell ref="A421:A422"/>
+    <mergeCell ref="A423:A424"/>
+    <mergeCell ref="A425:A426"/>
+    <mergeCell ref="A427:A428"/>
+    <mergeCell ref="A429:A430"/>
+    <mergeCell ref="A411:A412"/>
+    <mergeCell ref="A413:A414"/>
+    <mergeCell ref="A415:A416"/>
+    <mergeCell ref="A417:A418"/>
+    <mergeCell ref="A419:A420"/>
+    <mergeCell ref="A401:A402"/>
+    <mergeCell ref="A403:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="A407:A408"/>
+    <mergeCell ref="A409:A410"/>
+    <mergeCell ref="A391:A392"/>
+    <mergeCell ref="A393:A394"/>
+    <mergeCell ref="A395:A396"/>
+    <mergeCell ref="A397:A398"/>
+    <mergeCell ref="A399:A400"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="A383:A384"/>
+    <mergeCell ref="A385:A386"/>
+    <mergeCell ref="A387:A388"/>
+    <mergeCell ref="A389:A390"/>
+    <mergeCell ref="A371:A372"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="A375:A376"/>
+    <mergeCell ref="A377:A378"/>
+    <mergeCell ref="A379:A380"/>
+    <mergeCell ref="A367:A368"/>
+    <mergeCell ref="A369:A370"/>
+    <mergeCell ref="A364:I364"/>
+    <mergeCell ref="A365:I365"/>
+    <mergeCell ref="A352:A353"/>
+    <mergeCell ref="A354:A355"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A310:A311"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A264:A265"/>
+    <mergeCell ref="A266:A267"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="A241:L241"/>
+    <mergeCell ref="A242:L242"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="A225:A226"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
     <mergeCell ref="A1023:A1024"/>
     <mergeCell ref="A1025:A1026"/>
     <mergeCell ref="A4:A5"/>
@@ -25115,490 +25599,6 @@
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A140:L140"/>
-    <mergeCell ref="A141:L141"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="A225:A226"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="A241:L241"/>
-    <mergeCell ref="A242:L242"/>
-    <mergeCell ref="A264:A265"/>
-    <mergeCell ref="A266:A267"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A310:A311"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="A367:A368"/>
-    <mergeCell ref="A369:A370"/>
-    <mergeCell ref="A364:I364"/>
-    <mergeCell ref="A365:I365"/>
-    <mergeCell ref="A352:A353"/>
-    <mergeCell ref="A354:A355"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="A383:A384"/>
-    <mergeCell ref="A385:A386"/>
-    <mergeCell ref="A387:A388"/>
-    <mergeCell ref="A389:A390"/>
-    <mergeCell ref="A371:A372"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="A375:A376"/>
-    <mergeCell ref="A377:A378"/>
-    <mergeCell ref="A379:A380"/>
-    <mergeCell ref="A401:A402"/>
-    <mergeCell ref="A403:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="A407:A408"/>
-    <mergeCell ref="A409:A410"/>
-    <mergeCell ref="A391:A392"/>
-    <mergeCell ref="A393:A394"/>
-    <mergeCell ref="A395:A396"/>
-    <mergeCell ref="A397:A398"/>
-    <mergeCell ref="A399:A400"/>
-    <mergeCell ref="A421:A422"/>
-    <mergeCell ref="A423:A424"/>
-    <mergeCell ref="A425:A426"/>
-    <mergeCell ref="A427:A428"/>
-    <mergeCell ref="A429:A430"/>
-    <mergeCell ref="A411:A412"/>
-    <mergeCell ref="A413:A414"/>
-    <mergeCell ref="A415:A416"/>
-    <mergeCell ref="A417:A418"/>
-    <mergeCell ref="A419:A420"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="A431:A432"/>
-    <mergeCell ref="A433:A434"/>
-    <mergeCell ref="A435:A436"/>
-    <mergeCell ref="A437:A438"/>
-    <mergeCell ref="A441:I441"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="A484:A485"/>
-    <mergeCell ref="A486:A487"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="A522:A523"/>
-    <mergeCell ref="A526:I526"/>
-    <mergeCell ref="A527:I527"/>
-    <mergeCell ref="A529:A530"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="A514:A515"/>
-    <mergeCell ref="A516:A517"/>
-    <mergeCell ref="A518:A519"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="A541:A542"/>
-    <mergeCell ref="A543:A544"/>
-    <mergeCell ref="A545:A546"/>
-    <mergeCell ref="A547:A548"/>
-    <mergeCell ref="A549:A550"/>
-    <mergeCell ref="A531:A532"/>
-    <mergeCell ref="A533:A534"/>
-    <mergeCell ref="A535:A536"/>
-    <mergeCell ref="A537:A538"/>
-    <mergeCell ref="A539:A540"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="A563:A564"/>
-    <mergeCell ref="A565:A566"/>
-    <mergeCell ref="A567:A568"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="A551:A552"/>
-    <mergeCell ref="A553:A554"/>
-    <mergeCell ref="A555:A556"/>
-    <mergeCell ref="A557:A558"/>
-    <mergeCell ref="A559:A560"/>
-    <mergeCell ref="A581:A582"/>
-    <mergeCell ref="A583:A584"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="A587:A588"/>
-    <mergeCell ref="A589:A590"/>
-    <mergeCell ref="A571:A572"/>
-    <mergeCell ref="A573:A574"/>
-    <mergeCell ref="A575:A576"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="A579:A580"/>
-    <mergeCell ref="A601:A602"/>
-    <mergeCell ref="A603:A604"/>
-    <mergeCell ref="A605:A606"/>
-    <mergeCell ref="A607:A608"/>
-    <mergeCell ref="A609:A610"/>
-    <mergeCell ref="A591:A592"/>
-    <mergeCell ref="A593:A594"/>
-    <mergeCell ref="A595:A596"/>
-    <mergeCell ref="A597:A598"/>
-    <mergeCell ref="A599:A600"/>
-    <mergeCell ref="A621:A622"/>
-    <mergeCell ref="A623:A624"/>
-    <mergeCell ref="A625:A626"/>
-    <mergeCell ref="A627:A628"/>
-    <mergeCell ref="A629:A630"/>
-    <mergeCell ref="A611:A612"/>
-    <mergeCell ref="A613:A614"/>
-    <mergeCell ref="A615:A616"/>
-    <mergeCell ref="A617:A618"/>
-    <mergeCell ref="A619:A620"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="A644:A645"/>
-    <mergeCell ref="A646:A647"/>
-    <mergeCell ref="A648:A649"/>
-    <mergeCell ref="A650:A651"/>
-    <mergeCell ref="A631:A632"/>
-    <mergeCell ref="A635:I635"/>
-    <mergeCell ref="A636:I636"/>
-    <mergeCell ref="A638:A639"/>
-    <mergeCell ref="A640:A641"/>
-    <mergeCell ref="A662:A663"/>
-    <mergeCell ref="A664:A665"/>
-    <mergeCell ref="A666:A667"/>
-    <mergeCell ref="A668:A669"/>
-    <mergeCell ref="A670:A671"/>
-    <mergeCell ref="A652:A653"/>
-    <mergeCell ref="A654:A655"/>
-    <mergeCell ref="A656:A657"/>
-    <mergeCell ref="A658:A659"/>
-    <mergeCell ref="A660:A661"/>
-    <mergeCell ref="A682:A683"/>
-    <mergeCell ref="A684:A685"/>
-    <mergeCell ref="A686:A687"/>
-    <mergeCell ref="A688:A689"/>
-    <mergeCell ref="A690:A691"/>
-    <mergeCell ref="A672:A673"/>
-    <mergeCell ref="A674:A675"/>
-    <mergeCell ref="A676:A677"/>
-    <mergeCell ref="A678:A679"/>
-    <mergeCell ref="A680:A681"/>
-    <mergeCell ref="A702:A703"/>
-    <mergeCell ref="A704:A705"/>
-    <mergeCell ref="A706:A707"/>
-    <mergeCell ref="A708:A709"/>
-    <mergeCell ref="A710:A711"/>
-    <mergeCell ref="A692:A693"/>
-    <mergeCell ref="A694:A695"/>
-    <mergeCell ref="A696:A697"/>
-    <mergeCell ref="A698:A699"/>
-    <mergeCell ref="A700:A701"/>
-    <mergeCell ref="A722:A723"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="A728:I728"/>
-    <mergeCell ref="A729:I729"/>
-    <mergeCell ref="A731:A732"/>
-    <mergeCell ref="A712:A713"/>
-    <mergeCell ref="A714:A715"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="A718:A719"/>
-    <mergeCell ref="A720:A721"/>
-    <mergeCell ref="A743:A744"/>
-    <mergeCell ref="A745:A746"/>
-    <mergeCell ref="A747:A748"/>
-    <mergeCell ref="A749:A750"/>
-    <mergeCell ref="A751:A752"/>
-    <mergeCell ref="A733:A734"/>
-    <mergeCell ref="A735:A736"/>
-    <mergeCell ref="A737:A738"/>
-    <mergeCell ref="A739:A740"/>
-    <mergeCell ref="A741:A742"/>
-    <mergeCell ref="A763:A764"/>
-    <mergeCell ref="A765:A766"/>
-    <mergeCell ref="A767:A768"/>
-    <mergeCell ref="A769:A770"/>
-    <mergeCell ref="A753:A754"/>
-    <mergeCell ref="A755:A756"/>
-    <mergeCell ref="A757:A758"/>
-    <mergeCell ref="A759:A760"/>
-    <mergeCell ref="A761:A762"/>
-    <mergeCell ref="A780:A781"/>
-    <mergeCell ref="A782:A783"/>
-    <mergeCell ref="A784:A785"/>
-    <mergeCell ref="A786:A787"/>
-    <mergeCell ref="A788:A789"/>
-    <mergeCell ref="A776:A777"/>
-    <mergeCell ref="A778:A779"/>
-    <mergeCell ref="A773:I773"/>
-    <mergeCell ref="A774:I774"/>
-    <mergeCell ref="A800:A801"/>
-    <mergeCell ref="A802:A803"/>
-    <mergeCell ref="A804:A805"/>
-    <mergeCell ref="A806:A807"/>
-    <mergeCell ref="A808:A809"/>
-    <mergeCell ref="A790:A791"/>
-    <mergeCell ref="A792:A793"/>
-    <mergeCell ref="A794:A795"/>
-    <mergeCell ref="A796:A797"/>
-    <mergeCell ref="A798:A799"/>
-    <mergeCell ref="A820:A821"/>
-    <mergeCell ref="A822:A823"/>
-    <mergeCell ref="A824:A825"/>
-    <mergeCell ref="A826:A827"/>
-    <mergeCell ref="A828:A829"/>
-    <mergeCell ref="A810:A811"/>
-    <mergeCell ref="A812:A813"/>
-    <mergeCell ref="A814:A815"/>
-    <mergeCell ref="A816:A817"/>
-    <mergeCell ref="A818:A819"/>
-    <mergeCell ref="A840:A841"/>
-    <mergeCell ref="A842:A843"/>
-    <mergeCell ref="A844:A845"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="A848:A849"/>
-    <mergeCell ref="A830:A831"/>
-    <mergeCell ref="A832:A833"/>
-    <mergeCell ref="A834:A835"/>
-    <mergeCell ref="A836:A837"/>
-    <mergeCell ref="A838:A839"/>
-    <mergeCell ref="A860:A861"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="A864:A865"/>
-    <mergeCell ref="A866:A867"/>
-    <mergeCell ref="A868:A869"/>
-    <mergeCell ref="A850:A851"/>
-    <mergeCell ref="A852:A853"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="A856:A857"/>
-    <mergeCell ref="A858:A859"/>
-    <mergeCell ref="A891:A892"/>
-    <mergeCell ref="A886:L886"/>
-    <mergeCell ref="A887:L887"/>
-    <mergeCell ref="A893:A894"/>
-    <mergeCell ref="A895:A896"/>
-    <mergeCell ref="A880:A881"/>
-    <mergeCell ref="A882:A883"/>
-    <mergeCell ref="A889:A890"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="A872:A873"/>
-    <mergeCell ref="A874:A875"/>
-    <mergeCell ref="A876:A877"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="A907:A908"/>
-    <mergeCell ref="A909:A910"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="A913:A914"/>
-    <mergeCell ref="A915:A916"/>
-    <mergeCell ref="A897:A898"/>
-    <mergeCell ref="A899:A900"/>
-    <mergeCell ref="A901:A902"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="A905:A906"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="A929:A930"/>
-    <mergeCell ref="A931:A932"/>
-    <mergeCell ref="A933:A934"/>
-    <mergeCell ref="A935:A936"/>
-    <mergeCell ref="A917:A918"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="A921:A922"/>
-    <mergeCell ref="A923:A924"/>
-    <mergeCell ref="A925:A926"/>
-    <mergeCell ref="A947:A948"/>
-    <mergeCell ref="A949:A950"/>
-    <mergeCell ref="A951:A952"/>
-    <mergeCell ref="A953:A954"/>
-    <mergeCell ref="A955:A956"/>
-    <mergeCell ref="A937:A938"/>
-    <mergeCell ref="A939:A940"/>
-    <mergeCell ref="A941:A942"/>
-    <mergeCell ref="A943:A944"/>
-    <mergeCell ref="A945:A946"/>
-    <mergeCell ref="A967:A968"/>
-    <mergeCell ref="A969:A970"/>
-    <mergeCell ref="A971:A972"/>
-    <mergeCell ref="A973:A974"/>
-    <mergeCell ref="A957:A958"/>
-    <mergeCell ref="A959:A960"/>
-    <mergeCell ref="A961:A962"/>
-    <mergeCell ref="A963:A964"/>
-    <mergeCell ref="A965:A966"/>
-    <mergeCell ref="A985:A986"/>
-    <mergeCell ref="A987:A988"/>
-    <mergeCell ref="A989:A990"/>
-    <mergeCell ref="A991:A992"/>
-    <mergeCell ref="A993:A994"/>
-    <mergeCell ref="A975:A976"/>
-    <mergeCell ref="A977:A978"/>
-    <mergeCell ref="A979:A980"/>
-    <mergeCell ref="A981:A982"/>
-    <mergeCell ref="A983:A984"/>
-    <mergeCell ref="A1017:A1018"/>
-    <mergeCell ref="A1019:A1020"/>
-    <mergeCell ref="A1021:A1022"/>
-    <mergeCell ref="A1006:A1007"/>
-    <mergeCell ref="A1013:A1014"/>
-    <mergeCell ref="A1015:A1016"/>
-    <mergeCell ref="A1010:I1010"/>
-    <mergeCell ref="A1011:I1011"/>
-    <mergeCell ref="A995:A996"/>
-    <mergeCell ref="A997:A998"/>
-    <mergeCell ref="A1001:I1001"/>
-    <mergeCell ref="A1002:I1002"/>
-    <mergeCell ref="A1004:A1005"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -25670,7 +25670,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>1583</v>
       </c>
       <c r="B4" s="2"/>
@@ -25702,7 +25702,7 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -25777,7 +25777,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="17" t="s">
         <v>1586</v>
       </c>
       <c r="B13" s="2"/>
@@ -25809,7 +25809,7 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="15" t="s">
         <v>1589</v>
       </c>
       <c r="B15" s="8"/>
@@ -25837,7 +25837,7 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="15" t="s">
         <v>1591</v>
       </c>
       <c r="B17" s="8"/>
@@ -25869,7 +25869,7 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="15" t="s">
         <v>1593</v>
       </c>
       <c r="B19" s="8"/>
@@ -25901,7 +25901,7 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>1595</v>
       </c>
       <c r="B21" s="8"/>
@@ -25933,7 +25933,7 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="15" t="s">
         <v>1597</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -25967,7 +25967,7 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="15" t="s">
         <v>1601</v>
       </c>
       <c r="B25" s="8"/>
@@ -25999,7 +25999,7 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="15" t="s">
         <v>1604</v>
       </c>
       <c r="B27" s="8"/>
@@ -26027,7 +26027,7 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="15" t="s">
         <v>1606</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -26061,7 +26061,7 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="15" t="s">
         <v>1609</v>
       </c>
       <c r="B31" s="8"/>
@@ -26093,7 +26093,7 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="15" t="s">
         <v>1611</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -26127,7 +26127,7 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="15" t="s">
         <v>1615</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -26161,7 +26161,7 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="15" t="s">
         <v>1619</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -26195,7 +26195,7 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="15" t="s">
         <v>1622</v>
       </c>
       <c r="B39" s="8"/>
@@ -26227,7 +26227,7 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="15" t="s">
         <v>1624</v>
       </c>
       <c r="B41" s="8"/>
@@ -26259,7 +26259,7 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="15" t="s">
         <v>1626</v>
       </c>
       <c r="B43" s="8"/>
@@ -26291,7 +26291,7 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="15" t="s">
         <v>1628</v>
       </c>
       <c r="B45" s="8"/>
@@ -26323,7 +26323,7 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="15" t="s">
         <v>1630</v>
       </c>
       <c r="B47" s="8"/>
@@ -26355,7 +26355,7 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="15" t="s">
         <v>1632</v>
       </c>
       <c r="B49" s="8"/>
@@ -26387,7 +26387,7 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="15" t="s">
         <v>1634</v>
       </c>
       <c r="B51" s="8"/>
@@ -26419,7 +26419,7 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="15" t="s">
         <v>1636</v>
       </c>
       <c r="B53" s="8"/>
@@ -26447,7 +26447,7 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="15" t="s">
         <v>1638</v>
       </c>
       <c r="B55" s="8"/>
@@ -26479,7 +26479,7 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="15" t="s">
         <v>1640</v>
       </c>
       <c r="B57" s="8"/>
@@ -26511,7 +26511,7 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="15" t="s">
         <v>1642</v>
       </c>
       <c r="B59" s="8"/>
@@ -26543,7 +26543,7 @@
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="15" t="s">
         <v>1644</v>
       </c>
       <c r="B61" s="8"/>
@@ -26575,7 +26575,7 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="15" t="s">
         <v>1646</v>
       </c>
       <c r="B63" s="8"/>
@@ -26607,7 +26607,7 @@
       <c r="I64" s="7"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="15" t="s">
         <v>1648</v>
       </c>
       <c r="B65" s="8"/>
@@ -26639,7 +26639,7 @@
       <c r="I66" s="7"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="15" t="s">
         <v>1650</v>
       </c>
       <c r="B67" s="8"/>
@@ -26671,7 +26671,7 @@
       <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="15" t="s">
         <v>1652</v>
       </c>
       <c r="B69" s="8"/>
@@ -26703,7 +26703,7 @@
       <c r="I70" s="7"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="15" t="s">
         <v>1654</v>
       </c>
       <c r="B71" s="8"/>
@@ -26731,7 +26731,7 @@
       <c r="I72" s="7"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="15" t="s">
         <v>1656</v>
       </c>
       <c r="B73" s="8"/>
@@ -26763,7 +26763,7 @@
       <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="15" t="s">
         <v>1718</v>
       </c>
       <c r="B75" s="8"/>
@@ -26796,12 +26796,26 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
@@ -26814,26 +26828,12 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:I10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26913,7 +26913,7 @@
       <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>1659</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -26949,7 +26949,7 @@
       <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
         <v>1662</v>
       </c>
       <c r="B6" s="8"/>
@@ -26979,7 +26979,7 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="15" t="s">
         <v>1664</v>
       </c>
       <c r="B8" s="8"/>
@@ -27011,7 +27011,7 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="15" t="s">
         <v>1666</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -27045,7 +27045,7 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="15" t="s">
         <v>1669</v>
       </c>
       <c r="B12" s="8"/>
@@ -27077,7 +27077,7 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="15" t="s">
         <v>1671</v>
       </c>
       <c r="B14" s="8"/>
@@ -27109,7 +27109,7 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="15" t="s">
         <v>1673</v>
       </c>
       <c r="B16" s="8"/>
@@ -27141,7 +27141,7 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="15" t="s">
         <v>1675</v>
       </c>
       <c r="B18" s="8"/>
@@ -27173,7 +27173,7 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>1677</v>
       </c>
       <c r="B20" s="8"/>
@@ -27205,7 +27205,7 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>1679</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -27239,7 +27239,7 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="15" t="s">
         <v>1682</v>
       </c>
       <c r="B24" s="8"/>
@@ -27271,7 +27271,7 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="15" t="s">
         <v>1684</v>
       </c>
       <c r="B26" s="8"/>
@@ -27303,7 +27303,7 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="15" t="s">
         <v>1686</v>
       </c>
       <c r="B28" s="8"/>
@@ -27335,7 +27335,7 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="15" t="s">
         <v>1688</v>
       </c>
       <c r="B30" s="8"/>
@@ -27367,7 +27367,7 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="15" t="s">
         <v>1690</v>
       </c>
       <c r="B32" s="8"/>
@@ -27399,7 +27399,7 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="15" t="s">
         <v>1692</v>
       </c>
       <c r="B34" s="8"/>
@@ -27431,7 +27431,7 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="15" t="s">
         <v>1694</v>
       </c>
       <c r="B36" s="8"/>
@@ -27463,7 +27463,7 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="15" t="s">
         <v>1696</v>
       </c>
       <c r="B38" s="8"/>
@@ -27495,7 +27495,7 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="15" t="s">
         <v>1698</v>
       </c>
       <c r="B40" s="8"/>
@@ -27527,7 +27527,7 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="15" t="s">
         <v>1700</v>
       </c>
       <c r="B42" s="8"/>
@@ -27559,7 +27559,7 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="15" t="s">
         <v>1702</v>
       </c>
       <c r="B44" s="8"/>
@@ -27591,7 +27591,7 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="15" t="s">
         <v>1704</v>
       </c>
       <c r="B46" s="8"/>
@@ -27623,7 +27623,7 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="15" t="s">
         <v>1706</v>
       </c>
       <c r="B48" s="8"/>
@@ -27655,7 +27655,7 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="15" t="s">
         <v>1708</v>
       </c>
       <c r="B50" s="8"/>
@@ -27687,7 +27687,7 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="15" t="s">
         <v>1710</v>
       </c>
       <c r="B52" s="8"/>
@@ -27715,7 +27715,7 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="15" t="s">
         <v>1711</v>
       </c>
       <c r="B54" s="8"/>
@@ -27796,7 +27796,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="17" t="s">
         <v>1713</v>
       </c>
       <c r="B61" s="2"/>
@@ -27824,7 +27824,7 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="15" t="s">
         <v>1715</v>
       </c>
       <c r="B63" s="8"/>
@@ -27857,31 +27857,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A50:A51"/>
@@ -27889,6 +27864,31 @@
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
